--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -295,6 +295,9 @@
   </x:si>
   <x:si>
     <x:t>Saman Herath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hiuhuiih</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3575,6 +3578,20 @@
         <x:v>46254.112226713</x:v>
       </x:c>
     </x:row>
+    <x:row r="206" spans="1:4">
+      <x:c r="A206" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B206" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C206" s="6">
+        <x:v>88768687</x:v>
+      </x:c>
+      <x:c r="D206" s="7">
+        <x:v>46254.114283912</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -298,6 +298,9 @@
   </x:si>
   <x:si>
     <x:t>hiuhuiih</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jkhkhk</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3592,6 +3595,20 @@
         <x:v>46254.114283912</x:v>
       </x:c>
     </x:row>
+    <x:row r="207" spans="1:4">
+      <x:c r="A207" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B207" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C207" s="6">
+        <x:v>78798797</x:v>
+      </x:c>
+      <x:c r="D207" s="7">
+        <x:v>46254.1179897338</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -301,6 +301,15 @@
   </x:si>
   <x:si>
     <x:t>jkhkhk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hgjgjg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jhjvhjvj</x:t>
+  </x:si>
+  <x:si>
+    <x:t>879879</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3609,6 +3618,48 @@
         <x:v>46254.1179897338</x:v>
       </x:c>
     </x:row>
+    <x:row r="208" spans="1:4">
+      <x:c r="A208" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B208" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C208" s="6">
+        <x:v>888</x:v>
+      </x:c>
+      <x:c r="D208" s="7">
+        <x:v>46254.1226736806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:4">
+      <x:c r="A209" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B209" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C209" s="6">
+        <x:v>987979</x:v>
+      </x:c>
+      <x:c r="D209" s="7">
+        <x:v>46254.124480544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:4">
+      <x:c r="A210" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B210" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C210" s="6">
+        <x:v>8797798</x:v>
+      </x:c>
+      <x:c r="D210" s="7">
+        <x:v>46254.1265442014</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -310,6 +310,9 @@
   </x:si>
   <x:si>
     <x:t>879879</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jjjkh</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -716,7 +719,7 @@
   <x:cols>
     <x:col min="1" max="1" width="31.853482" style="0" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="9.996339" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="3" max="3" width="13.282054" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="3" max="3" width="14.282054" style="0" bestFit="1" customWidth="1"/>
     <x:col min="4" max="4" width="21.567768" style="2" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -3658,6 +3661,34 @@
       </x:c>
       <x:c r="D210" s="7">
         <x:v>46254.1265442014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:4">
+      <x:c r="A211" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B211" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C211" s="6">
+        <x:v>68768686</x:v>
+      </x:c>
+      <x:c r="D211" s="7">
+        <x:v>46254.1354002431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:4">
+      <x:c r="A212" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B212" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C212" s="6">
+        <x:v>779879797</x:v>
+      </x:c>
+      <x:c r="D212" s="7">
+        <x:v>46254.135708912</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -313,6 +313,15 @@
   </x:si>
   <x:si>
     <x:t>jjjkh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gugugiu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>uggjg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>kjhkhkh</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3691,6 +3700,48 @@
         <x:v>46254.135708912</x:v>
       </x:c>
     </x:row>
+    <x:row r="213" spans="1:4">
+      <x:c r="A213" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B213" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C213" s="6">
+        <x:v>887897</x:v>
+      </x:c>
+      <x:c r="D213" s="7">
+        <x:v>46254.139562662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:4">
+      <x:c r="A214" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B214" s="5">
+        <x:v>46246</x:v>
+      </x:c>
+      <x:c r="C214" s="6">
+        <x:v>86868</x:v>
+      </x:c>
+      <x:c r="D214" s="7">
+        <x:v>46254.1459667477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:4">
+      <x:c r="A215" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B215" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C215" s="6">
+        <x:v>9879879</x:v>
+      </x:c>
+      <x:c r="D215" s="7">
+        <x:v>46254.1527740856</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -322,6 +322,18 @@
   </x:si>
   <x:si>
     <x:t>kjhkhkh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>efefe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jdjdjjd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharaka</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tharak</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -3742,6 +3754,62 @@
         <x:v>46254.1527740856</x:v>
       </x:c>
     </x:row>
+    <x:row r="216" spans="1:4">
+      <x:c r="A216" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B216" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C216" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D216" s="7">
+        <x:v>46254.459009838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:4">
+      <x:c r="A217" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B217" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C217" s="6">
+        <x:v>33333</x:v>
+      </x:c>
+      <x:c r="D217" s="7">
+        <x:v>46254.4614965625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:4">
+      <x:c r="A218" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B218" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C218" s="6">
+        <x:v>2222</x:v>
+      </x:c>
+      <x:c r="D218" s="7">
+        <x:v>46254.4625665972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:4">
+      <x:c r="A219" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B219" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C219" s="6">
+        <x:v>19999.79</x:v>
+      </x:c>
+      <x:c r="D219" s="7">
+        <x:v>46254.467962338</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -3810,6 +3810,34 @@
         <x:v>46254.467962338</x:v>
       </x:c>
     </x:row>
+    <x:row r="220" spans="1:4">
+      <x:c r="A220" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B220" s="5">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="C220" s="6">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="D220" s="7">
+        <x:v>46254.4767984491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:4">
+      <x:c r="A221" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B221" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C221" s="6">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="D221" s="7">
+        <x:v>46254.4796984607</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -3838,6 +3838,9806 @@
         <x:v>46254.4796984607</x:v>
       </x:c>
     </x:row>
+    <x:row r="222" spans="1:4">
+      <x:c r="A222" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B222" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C222" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D222" s="7">
+        <x:v>46254.4955566088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:4">
+      <x:c r="A223" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B223" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C223" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D223" s="7">
+        <x:v>46254.495568588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:4">
+      <x:c r="A224" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B224" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C224" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D224" s="7">
+        <x:v>46254.4955717245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:4">
+      <x:c r="A225" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B225" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C225" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D225" s="7">
+        <x:v>46254.4955738889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:4">
+      <x:c r="A226" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B226" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C226" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D226" s="7">
+        <x:v>46254.4955762153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:4">
+      <x:c r="A227" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B227" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C227" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D227" s="7">
+        <x:v>46254.4955784028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="228" spans="1:4">
+      <x:c r="A228" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B228" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C228" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D228" s="7">
+        <x:v>46254.4955802894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="229" spans="1:4">
+      <x:c r="A229" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B229" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C229" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D229" s="7">
+        <x:v>46254.4955827662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="230" spans="1:4">
+      <x:c r="A230" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B230" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C230" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D230" s="7">
+        <x:v>46254.4955852662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="231" spans="1:4">
+      <x:c r="A231" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B231" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C231" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D231" s="7">
+        <x:v>46254.4955878125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="232" spans="1:4">
+      <x:c r="A232" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B232" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C232" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D232" s="7">
+        <x:v>46254.4955909607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:4">
+      <x:c r="A233" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B233" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C233" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D233" s="7">
+        <x:v>46254.495593206</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:4">
+      <x:c r="A234" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B234" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C234" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D234" s="7">
+        <x:v>46254.4955947685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:4">
+      <x:c r="A235" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B235" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C235" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D235" s="7">
+        <x:v>46254.4955971991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:4">
+      <x:c r="A236" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B236" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C236" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D236" s="7">
+        <x:v>46254.4955996412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:4">
+      <x:c r="A237" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B237" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C237" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D237" s="7">
+        <x:v>46254.495601794</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:4">
+      <x:c r="A238" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B238" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C238" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D238" s="7">
+        <x:v>46254.4956037963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:4">
+      <x:c r="A239" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B239" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C239" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D239" s="7">
+        <x:v>46254.495605706</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:4">
+      <x:c r="A240" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B240" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C240" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D240" s="7">
+        <x:v>46254.4956074768</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:4">
+      <x:c r="A241" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B241" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C241" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D241" s="7">
+        <x:v>46254.4956089468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:4">
+      <x:c r="A242" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B242" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C242" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D242" s="7">
+        <x:v>46254.4956108218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:4">
+      <x:c r="A243" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B243" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C243" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D243" s="7">
+        <x:v>46254.4956134028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:4">
+      <x:c r="A244" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B244" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C244" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D244" s="7">
+        <x:v>46254.4956151736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:4">
+      <x:c r="A245" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B245" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C245" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D245" s="7">
+        <x:v>46254.4956173495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:4">
+      <x:c r="A246" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B246" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C246" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D246" s="7">
+        <x:v>46254.4956189468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:4">
+      <x:c r="A247" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B247" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C247" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D247" s="7">
+        <x:v>46254.4956210185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:4">
+      <x:c r="A248" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B248" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C248" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D248" s="7">
+        <x:v>46254.495622581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:4">
+      <x:c r="A249" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B249" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C249" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D249" s="7">
+        <x:v>46254.4956239005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:4">
+      <x:c r="A250" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B250" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C250" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D250" s="7">
+        <x:v>46254.4956260995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:4">
+      <x:c r="A251" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B251" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C251" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D251" s="7">
+        <x:v>46254.4956281944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:4">
+      <x:c r="A252" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B252" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C252" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D252" s="7">
+        <x:v>46254.4956298843</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:4">
+      <x:c r="A253" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B253" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C253" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D253" s="7">
+        <x:v>46254.4956315856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:4">
+      <x:c r="A254" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B254" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C254" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D254" s="7">
+        <x:v>46254.4956340162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:4">
+      <x:c r="A255" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B255" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C255" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D255" s="7">
+        <x:v>46254.4956360995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:4">
+      <x:c r="A256" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B256" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C256" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D256" s="7">
+        <x:v>46254.4956376505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:4">
+      <x:c r="A257" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B257" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C257" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D257" s="7">
+        <x:v>46254.4956392477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:4">
+      <x:c r="A258" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B258" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C258" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D258" s="7">
+        <x:v>46254.4956409722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:4">
+      <x:c r="A259" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B259" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C259" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D259" s="7">
+        <x:v>46254.4956426852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:4">
+      <x:c r="A260" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B260" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C260" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D260" s="7">
+        <x:v>46254.4956445486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:4">
+      <x:c r="A261" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B261" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C261" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D261" s="7">
+        <x:v>46254.4956460648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:4">
+      <x:c r="A262" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B262" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C262" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D262" s="7">
+        <x:v>46254.4956472106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:4">
+      <x:c r="A263" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B263" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C263" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D263" s="7">
+        <x:v>46254.4956483681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:4">
+      <x:c r="A264" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B264" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C264" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D264" s="7">
+        <x:v>46254.4956495949</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:4">
+      <x:c r="A265" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B265" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C265" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D265" s="7">
+        <x:v>46254.4956504282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:4">
+      <x:c r="A266" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B266" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C266" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D266" s="7">
+        <x:v>46254.4956516319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:4">
+      <x:c r="A267" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B267" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C267" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D267" s="7">
+        <x:v>46254.4956526273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:4">
+      <x:c r="A268" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B268" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C268" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D268" s="7">
+        <x:v>46254.4956537847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:4">
+      <x:c r="A269" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B269" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C269" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D269" s="7">
+        <x:v>46254.4956550926</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:4">
+      <x:c r="A270" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B270" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C270" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D270" s="7">
+        <x:v>46254.4956563079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:4">
+      <x:c r="A271" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B271" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C271" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D271" s="7">
+        <x:v>46254.4956573611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:4">
+      <x:c r="A272" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B272" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C272" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D272" s="7">
+        <x:v>46254.4956582407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:4">
+      <x:c r="A273" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B273" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C273" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D273" s="7">
+        <x:v>46254.4956591551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:4">
+      <x:c r="A274" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B274" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C274" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D274" s="7">
+        <x:v>46254.4956602546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:4">
+      <x:c r="A275" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B275" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C275" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D275" s="7">
+        <x:v>46254.4956611227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:4">
+      <x:c r="A276" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B276" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C276" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D276" s="7">
+        <x:v>46254.4956634375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:4">
+      <x:c r="A277" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B277" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C277" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D277" s="7">
+        <x:v>46254.4956643287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:4">
+      <x:c r="A278" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B278" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C278" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D278" s="7">
+        <x:v>46254.4956651042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:4">
+      <x:c r="A279" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B279" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C279" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D279" s="7">
+        <x:v>46254.4956658449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:4">
+      <x:c r="A280" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B280" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C280" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D280" s="7">
+        <x:v>46254.4956665046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:4">
+      <x:c r="A281" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B281" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C281" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D281" s="7">
+        <x:v>46254.4956672917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="282" spans="1:4">
+      <x:c r="A282" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B282" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C282" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D282" s="7">
+        <x:v>46254.4956681944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:4">
+      <x:c r="A283" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B283" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C283" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D283" s="7">
+        <x:v>46254.4956691782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:4">
+      <x:c r="A284" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B284" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C284" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D284" s="7">
+        <x:v>46254.4956699884</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:4">
+      <x:c r="A285" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B285" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C285" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D285" s="7">
+        <x:v>46254.4956707639</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:4">
+      <x:c r="A286" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B286" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C286" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D286" s="7">
+        <x:v>46254.4956720255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:4">
+      <x:c r="A287" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B287" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C287" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D287" s="7">
+        <x:v>46254.4956730556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:4">
+      <x:c r="A288" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B288" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C288" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D288" s="7">
+        <x:v>46254.4956740509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:4">
+      <x:c r="A289" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B289" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C289" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D289" s="7">
+        <x:v>46254.4956748148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:4">
+      <x:c r="A290" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B290" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C290" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D290" s="7">
+        <x:v>46254.4956757176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:4">
+      <x:c r="A291" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B291" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C291" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D291" s="7">
+        <x:v>46254.4956767824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:4">
+      <x:c r="A292" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B292" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C292" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D292" s="7">
+        <x:v>46254.4956774306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:4">
+      <x:c r="A293" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B293" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C293" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D293" s="7">
+        <x:v>46254.4956781944</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:4">
+      <x:c r="A294" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B294" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C294" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D294" s="7">
+        <x:v>46254.4956789815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:4">
+      <x:c r="A295" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B295" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C295" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D295" s="7">
+        <x:v>46254.4956796528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:4">
+      <x:c r="A296" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B296" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C296" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D296" s="7">
+        <x:v>46254.4956804398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:4">
+      <x:c r="A297" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B297" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C297" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D297" s="7">
+        <x:v>46254.4956812616</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:4">
+      <x:c r="A298" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B298" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C298" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D298" s="7">
+        <x:v>46254.4956821991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:4">
+      <x:c r="A299" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B299" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C299" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D299" s="7">
+        <x:v>46254.4956829977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:4">
+      <x:c r="A300" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B300" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C300" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D300" s="7">
+        <x:v>46254.4956841435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:4">
+      <x:c r="A301" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B301" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C301" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D301" s="7">
+        <x:v>46254.4956848495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:4">
+      <x:c r="A302" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B302" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C302" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D302" s="7">
+        <x:v>46254.4956855556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:4">
+      <x:c r="A303" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B303" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C303" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D303" s="7">
+        <x:v>46254.4956866898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:4">
+      <x:c r="A304" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B304" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C304" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D304" s="7">
+        <x:v>46254.4956874421</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:4">
+      <x:c r="A305" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B305" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C305" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D305" s="7">
+        <x:v>46254.4956882292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:4">
+      <x:c r="A306" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B306" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C306" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D306" s="7">
+        <x:v>46254.4956891898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:4">
+      <x:c r="A307" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B307" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C307" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D307" s="7">
+        <x:v>46254.4956899769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:4">
+      <x:c r="A308" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B308" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C308" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D308" s="7">
+        <x:v>46254.4956911574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:4">
+      <x:c r="A309" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B309" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C309" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D309" s="7">
+        <x:v>46254.4956921296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:4">
+      <x:c r="A310" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B310" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C310" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D310" s="7">
+        <x:v>46254.4956928009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:4">
+      <x:c r="A311" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B311" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C311" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D311" s="7">
+        <x:v>46254.4956934259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:4">
+      <x:c r="A312" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B312" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C312" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D312" s="7">
+        <x:v>46254.495694294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:4">
+      <x:c r="A313" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B313" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C313" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D313" s="7">
+        <x:v>46254.4956950231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:4">
+      <x:c r="A314" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B314" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C314" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D314" s="7">
+        <x:v>46254.4956957755</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:4">
+      <x:c r="A315" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B315" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C315" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D315" s="7">
+        <x:v>46254.4956970255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:4">
+      <x:c r="A316" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B316" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C316" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D316" s="7">
+        <x:v>46254.4956976852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:4">
+      <x:c r="A317" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B317" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C317" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D317" s="7">
+        <x:v>46254.4956994676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:4">
+      <x:c r="A318" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B318" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C318" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D318" s="7">
+        <x:v>46254.4957003935</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:4">
+      <x:c r="A319" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B319" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C319" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D319" s="7">
+        <x:v>46254.4957013426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:4">
+      <x:c r="A320" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B320" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C320" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D320" s="7">
+        <x:v>46254.4957023495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:4">
+      <x:c r="A321" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B321" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C321" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D321" s="7">
+        <x:v>46254.4957030903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:4">
+      <x:c r="A322" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B322" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C322" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D322" s="7">
+        <x:v>46254.4968180787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:4">
+      <x:c r="A323" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B323" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C323" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D323" s="7">
+        <x:v>46254.4968189352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:4">
+      <x:c r="A324" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B324" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C324" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D324" s="7">
+        <x:v>46254.4968196296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:4">
+      <x:c r="A325" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B325" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C325" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D325" s="7">
+        <x:v>46254.4968204514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:4">
+      <x:c r="A326" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B326" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C326" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D326" s="7">
+        <x:v>46254.4968213889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:4">
+      <x:c r="A327" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B327" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C327" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D327" s="7">
+        <x:v>46254.4968222106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:4">
+      <x:c r="A328" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B328" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C328" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D328" s="7">
+        <x:v>46254.4968229398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:4">
+      <x:c r="A329" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B329" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C329" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D329" s="7">
+        <x:v>46254.4968234491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:4">
+      <x:c r="A330" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B330" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C330" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D330" s="7">
+        <x:v>46254.4968239931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:4">
+      <x:c r="A331" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B331" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C331" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D331" s="7">
+        <x:v>46254.4968245833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:4">
+      <x:c r="A332" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B332" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C332" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D332" s="7">
+        <x:v>46254.4968251736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:4">
+      <x:c r="A333" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B333" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C333" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D333" s="7">
+        <x:v>46254.4968259028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:4">
+      <x:c r="A334" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B334" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C334" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D334" s="7">
+        <x:v>46254.4968268056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:4">
+      <x:c r="A335" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B335" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C335" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D335" s="7">
+        <x:v>46254.4968276042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:4">
+      <x:c r="A336" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B336" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C336" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D336" s="7">
+        <x:v>46254.4968282755</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:4">
+      <x:c r="A337" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B337" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C337" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D337" s="7">
+        <x:v>46254.4968291782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:4">
+      <x:c r="A338" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B338" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C338" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D338" s="7">
+        <x:v>46254.4968300347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:4">
+      <x:c r="A339" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B339" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C339" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D339" s="7">
+        <x:v>46254.4968306829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:4">
+      <x:c r="A340" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B340" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C340" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D340" s="7">
+        <x:v>46254.4968314236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:4">
+      <x:c r="A341" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B341" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C341" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D341" s="7">
+        <x:v>46254.4968321528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:4">
+      <x:c r="A342" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B342" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C342" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D342" s="7">
+        <x:v>46254.4968329861</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:4">
+      <x:c r="A343" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B343" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C343" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D343" s="7">
+        <x:v>46254.4968337963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:4">
+      <x:c r="A344" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B344" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C344" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D344" s="7">
+        <x:v>46254.4968347685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:4">
+      <x:c r="A345" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B345" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C345" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D345" s="7">
+        <x:v>46254.496835544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:4">
+      <x:c r="A346" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B346" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C346" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D346" s="7">
+        <x:v>46254.4968363194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:4">
+      <x:c r="A347" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B347" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C347" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D347" s="7">
+        <x:v>46254.496836956</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:4">
+      <x:c r="A348" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B348" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C348" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D348" s="7">
+        <x:v>46254.4968374537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:4">
+      <x:c r="A349" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B349" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C349" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D349" s="7">
+        <x:v>46254.4968380787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:4">
+      <x:c r="A350" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B350" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C350" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D350" s="7">
+        <x:v>46254.4968387963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:4">
+      <x:c r="A351" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B351" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C351" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D351" s="7">
+        <x:v>46254.4968396296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:4">
+      <x:c r="A352" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B352" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C352" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D352" s="7">
+        <x:v>46254.4968404167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:4">
+      <x:c r="A353" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B353" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C353" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D353" s="7">
+        <x:v>46254.4968412616</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:4">
+      <x:c r="A354" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B354" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C354" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D354" s="7">
+        <x:v>46254.4968420139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:4">
+      <x:c r="A355" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B355" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C355" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D355" s="7">
+        <x:v>46254.4968427546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:4">
+      <x:c r="A356" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B356" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C356" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D356" s="7">
+        <x:v>46254.4968435185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:4">
+      <x:c r="A357" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B357" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C357" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D357" s="7">
+        <x:v>46254.4968443171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:4">
+      <x:c r="A358" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B358" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C358" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D358" s="7">
+        <x:v>46254.496845</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:4">
+      <x:c r="A359" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B359" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C359" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D359" s="7">
+        <x:v>46254.4968456713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="360" spans="1:4">
+      <x:c r="A360" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B360" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C360" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D360" s="7">
+        <x:v>46254.4968465162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="361" spans="1:4">
+      <x:c r="A361" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B361" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C361" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D361" s="7">
+        <x:v>46254.496847338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="362" spans="1:4">
+      <x:c r="A362" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B362" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C362" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D362" s="7">
+        <x:v>46254.4968480787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="363" spans="1:4">
+      <x:c r="A363" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B363" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C363" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D363" s="7">
+        <x:v>46254.4968490278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="364" spans="1:4">
+      <x:c r="A364" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B364" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C364" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D364" s="7">
+        <x:v>46254.4968497106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="365" spans="1:4">
+      <x:c r="A365" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B365" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C365" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D365" s="7">
+        <x:v>46254.4968504398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="366" spans="1:4">
+      <x:c r="A366" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B366" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C366" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D366" s="7">
+        <x:v>46254.4968511227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="367" spans="1:4">
+      <x:c r="A367" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B367" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C367" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D367" s="7">
+        <x:v>46254.4968518403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="368" spans="1:4">
+      <x:c r="A368" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B368" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C368" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D368" s="7">
+        <x:v>46254.4968525579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="369" spans="1:4">
+      <x:c r="A369" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B369" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C369" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D369" s="7">
+        <x:v>46254.4968535185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="370" spans="1:4">
+      <x:c r="A370" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B370" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C370" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D370" s="7">
+        <x:v>46254.4968544213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="371" spans="1:4">
+      <x:c r="A371" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B371" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C371" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D371" s="7">
+        <x:v>46254.4968551042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="372" spans="1:4">
+      <x:c r="A372" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B372" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C372" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D372" s="7">
+        <x:v>46254.4968560417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="373" spans="1:4">
+      <x:c r="A373" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B373" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C373" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D373" s="7">
+        <x:v>46254.4968571875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="374" spans="1:4">
+      <x:c r="A374" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B374" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C374" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D374" s="7">
+        <x:v>46254.4968579861</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="375" spans="1:4">
+      <x:c r="A375" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B375" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C375" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D375" s="7">
+        <x:v>46254.496858831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="376" spans="1:4">
+      <x:c r="A376" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B376" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C376" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D376" s="7">
+        <x:v>46254.4968596181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="377" spans="1:4">
+      <x:c r="A377" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B377" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C377" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D377" s="7">
+        <x:v>46254.4968604282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="378" spans="1:4">
+      <x:c r="A378" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B378" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C378" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D378" s="7">
+        <x:v>46254.4968612847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="379" spans="1:4">
+      <x:c r="A379" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B379" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C379" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D379" s="7">
+        <x:v>46254.4968622222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="380" spans="1:4">
+      <x:c r="A380" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B380" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C380" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D380" s="7">
+        <x:v>46254.4968630556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="381" spans="1:4">
+      <x:c r="A381" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B381" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C381" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D381" s="7">
+        <x:v>46254.4968640856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="382" spans="1:4">
+      <x:c r="A382" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B382" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C382" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D382" s="7">
+        <x:v>46254.4968646644</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="383" spans="1:4">
+      <x:c r="A383" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B383" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C383" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D383" s="7">
+        <x:v>46254.4968652778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="384" spans="1:4">
+      <x:c r="A384" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B384" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C384" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D384" s="7">
+        <x:v>46254.4968659028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="385" spans="1:4">
+      <x:c r="A385" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B385" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C385" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D385" s="7">
+        <x:v>46254.4968667593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="386" spans="1:4">
+      <x:c r="A386" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B386" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C386" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D386" s="7">
+        <x:v>46254.4968676157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="387" spans="1:4">
+      <x:c r="A387" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B387" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C387" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D387" s="7">
+        <x:v>46254.4968685301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="388" spans="1:4">
+      <x:c r="A388" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B388" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C388" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D388" s="7">
+        <x:v>46254.4968694676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="389" spans="1:4">
+      <x:c r="A389" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B389" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C389" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D389" s="7">
+        <x:v>46254.4968702546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="390" spans="1:4">
+      <x:c r="A390" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B390" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C390" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D390" s="7">
+        <x:v>46254.4968711574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="391" spans="1:4">
+      <x:c r="A391" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B391" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C391" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D391" s="7">
+        <x:v>46254.4968719676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="392" spans="1:4">
+      <x:c r="A392" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B392" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C392" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D392" s="7">
+        <x:v>46254.4968729051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="393" spans="1:4">
+      <x:c r="A393" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B393" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C393" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D393" s="7">
+        <x:v>46254.4968737731</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="394" spans="1:4">
+      <x:c r="A394" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B394" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C394" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D394" s="7">
+        <x:v>46254.4968746181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="395" spans="1:4">
+      <x:c r="A395" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B395" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C395" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D395" s="7">
+        <x:v>46254.4968755671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="396" spans="1:4">
+      <x:c r="A396" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B396" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C396" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D396" s="7">
+        <x:v>46254.4968764236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="397" spans="1:4">
+      <x:c r="A397" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B397" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C397" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D397" s="7">
+        <x:v>46254.4968772454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="398" spans="1:4">
+      <x:c r="A398" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B398" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C398" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D398" s="7">
+        <x:v>46254.4968779977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="399" spans="1:4">
+      <x:c r="A399" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B399" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C399" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D399" s="7">
+        <x:v>46254.4968785301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="400" spans="1:4">
+      <x:c r="A400" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B400" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C400" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D400" s="7">
+        <x:v>46254.4968791319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="401" spans="1:4">
+      <x:c r="A401" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B401" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C401" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D401" s="7">
+        <x:v>46254.4968799537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="402" spans="1:4">
+      <x:c r="A402" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B402" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C402" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D402" s="7">
+        <x:v>46254.4968807176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="403" spans="1:4">
+      <x:c r="A403" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B403" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C403" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D403" s="7">
+        <x:v>46254.4968814352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="404" spans="1:4">
+      <x:c r="A404" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B404" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C404" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D404" s="7">
+        <x:v>46254.4968823611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="405" spans="1:4">
+      <x:c r="A405" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B405" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C405" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D405" s="7">
+        <x:v>46254.4968831713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="406" spans="1:4">
+      <x:c r="A406" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B406" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C406" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D406" s="7">
+        <x:v>46254.4968839352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="407" spans="1:4">
+      <x:c r="A407" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B407" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C407" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D407" s="7">
+        <x:v>46254.4968847454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="408" spans="1:4">
+      <x:c r="A408" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B408" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C408" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D408" s="7">
+        <x:v>46254.4968853588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="409" spans="1:4">
+      <x:c r="A409" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B409" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C409" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D409" s="7">
+        <x:v>46254.4968861343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="410" spans="1:4">
+      <x:c r="A410" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B410" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C410" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D410" s="7">
+        <x:v>46254.4968871296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="411" spans="1:4">
+      <x:c r="A411" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B411" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C411" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D411" s="7">
+        <x:v>46254.4968880671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="412" spans="1:4">
+      <x:c r="A412" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B412" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C412" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D412" s="7">
+        <x:v>46254.4968889236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="413" spans="1:4">
+      <x:c r="A413" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B413" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C413" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D413" s="7">
+        <x:v>46254.4968899074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="414" spans="1:4">
+      <x:c r="A414" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B414" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C414" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D414" s="7">
+        <x:v>46254.4968907523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="415" spans="1:4">
+      <x:c r="A415" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B415" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C415" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D415" s="7">
+        <x:v>46254.4968915972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="416" spans="1:4">
+      <x:c r="A416" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B416" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C416" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D416" s="7">
+        <x:v>46254.4968924421</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="417" spans="1:4">
+      <x:c r="A417" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B417" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C417" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D417" s="7">
+        <x:v>46254.4968932639</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="418" spans="1:4">
+      <x:c r="A418" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B418" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C418" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D418" s="7">
+        <x:v>46254.4968940278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="419" spans="1:4">
+      <x:c r="A419" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B419" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C419" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D419" s="7">
+        <x:v>46254.4968951273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="420" spans="1:4">
+      <x:c r="A420" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B420" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C420" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D420" s="7">
+        <x:v>46254.4968960301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="421" spans="1:4">
+      <x:c r="A421" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B421" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C421" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D421" s="7">
+        <x:v>46254.4968970486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="422" spans="1:4">
+      <x:c r="A422" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B422" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C422" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D422" s="7">
+        <x:v>46254.4980701042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="423" spans="1:4">
+      <x:c r="A423" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B423" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C423" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D423" s="7">
+        <x:v>46254.4980707523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="424" spans="1:4">
+      <x:c r="A424" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B424" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C424" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D424" s="7">
+        <x:v>46254.4980715857</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="425" spans="1:4">
+      <x:c r="A425" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B425" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C425" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D425" s="7">
+        <x:v>46254.4980725579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="426" spans="1:4">
+      <x:c r="A426" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B426" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C426" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D426" s="7">
+        <x:v>46254.4980733796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="427" spans="1:4">
+      <x:c r="A427" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B427" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C427" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D427" s="7">
+        <x:v>46254.498074537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="428" spans="1:4">
+      <x:c r="A428" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B428" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C428" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D428" s="7">
+        <x:v>46254.4980754282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="429" spans="1:4">
+      <x:c r="A429" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B429" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C429" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D429" s="7">
+        <x:v>46254.4980762847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="430" spans="1:4">
+      <x:c r="A430" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B430" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C430" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D430" s="7">
+        <x:v>46254.4980772222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="431" spans="1:4">
+      <x:c r="A431" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B431" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C431" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D431" s="7">
+        <x:v>46254.4980781366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="432" spans="1:4">
+      <x:c r="A432" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B432" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C432" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D432" s="7">
+        <x:v>46254.4980791435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="433" spans="1:4">
+      <x:c r="A433" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B433" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C433" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D433" s="7">
+        <x:v>46254.4980801852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="434" spans="1:4">
+      <x:c r="A434" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B434" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C434" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D434" s="7">
+        <x:v>46254.4980810648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="435" spans="1:4">
+      <x:c r="A435" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B435" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C435" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D435" s="7">
+        <x:v>46254.4980820833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="436" spans="1:4">
+      <x:c r="A436" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B436" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C436" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D436" s="7">
+        <x:v>46254.4980827778</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="437" spans="1:4">
+      <x:c r="A437" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B437" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C437" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D437" s="7">
+        <x:v>46254.4980834606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="438" spans="1:4">
+      <x:c r="A438" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B438" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C438" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D438" s="7">
+        <x:v>46254.4980840972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="439" spans="1:4">
+      <x:c r="A439" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B439" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C439" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D439" s="7">
+        <x:v>46254.4980849769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="440" spans="1:4">
+      <x:c r="A440" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B440" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C440" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D440" s="7">
+        <x:v>46254.4980859722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="441" spans="1:4">
+      <x:c r="A441" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B441" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C441" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D441" s="7">
+        <x:v>46254.4980870833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="442" spans="1:4">
+      <x:c r="A442" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B442" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C442" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D442" s="7">
+        <x:v>46254.4980879514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="443" spans="1:4">
+      <x:c r="A443" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B443" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C443" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D443" s="7">
+        <x:v>46254.4980888079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="444" spans="1:4">
+      <x:c r="A444" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B444" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C444" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D444" s="7">
+        <x:v>46254.4980899306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="445" spans="1:4">
+      <x:c r="A445" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B445" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C445" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D445" s="7">
+        <x:v>46254.4980908449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="446" spans="1:4">
+      <x:c r="A446" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B446" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C446" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D446" s="7">
+        <x:v>46254.498091875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="447" spans="1:4">
+      <x:c r="A447" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B447" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C447" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D447" s="7">
+        <x:v>46254.4980928472</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="448" spans="1:4">
+      <x:c r="A448" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B448" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C448" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D448" s="7">
+        <x:v>46254.4980937847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="449" spans="1:4">
+      <x:c r="A449" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B449" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C449" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D449" s="7">
+        <x:v>46254.4980948495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="450" spans="1:4">
+      <x:c r="A450" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B450" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C450" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D450" s="7">
+        <x:v>46254.4980957523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="451" spans="1:4">
+      <x:c r="A451" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B451" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C451" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D451" s="7">
+        <x:v>46254.4980966435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="452" spans="1:4">
+      <x:c r="A452" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B452" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C452" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D452" s="7">
+        <x:v>46254.4980972569</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="453" spans="1:4">
+      <x:c r="A453" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B453" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C453" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D453" s="7">
+        <x:v>46254.4980978241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="454" spans="1:4">
+      <x:c r="A454" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B454" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C454" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D454" s="7">
+        <x:v>46254.4980983681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="455" spans="1:4">
+      <x:c r="A455" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B455" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C455" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D455" s="7">
+        <x:v>46254.4980988889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="456" spans="1:4">
+      <x:c r="A456" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B456" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C456" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D456" s="7">
+        <x:v>46254.4980995139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="457" spans="1:4">
+      <x:c r="A457" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B457" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C457" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D457" s="7">
+        <x:v>46254.4981003009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="458" spans="1:4">
+      <x:c r="A458" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B458" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C458" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D458" s="7">
+        <x:v>46254.4981012037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="459" spans="1:4">
+      <x:c r="A459" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B459" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C459" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D459" s="7">
+        <x:v>46254.4981022338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="460" spans="1:4">
+      <x:c r="A460" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B460" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C460" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D460" s="7">
+        <x:v>46254.498103287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461" spans="1:4">
+      <x:c r="A461" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B461" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C461" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D461" s="7">
+        <x:v>46254.4981042361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:4">
+      <x:c r="A462" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B462" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C462" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D462" s="7">
+        <x:v>46254.4981052315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="463" spans="1:4">
+      <x:c r="A463" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B463" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C463" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D463" s="7">
+        <x:v>46254.4981062731</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="464" spans="1:4">
+      <x:c r="A464" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B464" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C464" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D464" s="7">
+        <x:v>46254.4981077431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="465" spans="1:4">
+      <x:c r="A465" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B465" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C465" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D465" s="7">
+        <x:v>46254.4981086458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="466" spans="1:4">
+      <x:c r="A466" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B466" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C466" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D466" s="7">
+        <x:v>46254.498109838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="467" spans="1:4">
+      <x:c r="A467" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B467" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C467" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D467" s="7">
+        <x:v>46254.4981106713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="468" spans="1:4">
+      <x:c r="A468" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B468" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C468" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D468" s="7">
+        <x:v>46254.4981115162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="469" spans="1:4">
+      <x:c r="A469" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B469" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C469" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D469" s="7">
+        <x:v>46254.4981123032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="470" spans="1:4">
+      <x:c r="A470" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B470" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C470" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D470" s="7">
+        <x:v>46254.4981130903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="471" spans="1:4">
+      <x:c r="A471" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B471" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C471" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D471" s="7">
+        <x:v>46254.4981139931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="472" spans="1:4">
+      <x:c r="A472" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B472" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C472" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D472" s="7">
+        <x:v>46254.4981150579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="473" spans="1:4">
+      <x:c r="A473" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B473" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C473" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D473" s="7">
+        <x:v>46254.4981158912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="474" spans="1:4">
+      <x:c r="A474" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B474" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C474" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D474" s="7">
+        <x:v>46254.4981169676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="475" spans="1:4">
+      <x:c r="A475" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B475" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C475" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D475" s="7">
+        <x:v>46254.4981179398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="476" spans="1:4">
+      <x:c r="A476" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B476" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C476" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D476" s="7">
+        <x:v>46254.4981186574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="477" spans="1:4">
+      <x:c r="A477" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B477" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C477" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D477" s="7">
+        <x:v>46254.4981198958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="478" spans="1:4">
+      <x:c r="A478" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B478" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C478" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D478" s="7">
+        <x:v>46254.4981207176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="479" spans="1:4">
+      <x:c r="A479" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B479" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C479" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D479" s="7">
+        <x:v>46254.4981217245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="480" spans="1:4">
+      <x:c r="A480" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B480" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C480" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D480" s="7">
+        <x:v>46254.4981226389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="481" spans="1:4">
+      <x:c r="A481" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B481" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C481" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D481" s="7">
+        <x:v>46254.4981236111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="482" spans="1:4">
+      <x:c r="A482" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B482" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C482" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D482" s="7">
+        <x:v>46254.4981247569</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="483" spans="1:4">
+      <x:c r="A483" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B483" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C483" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D483" s="7">
+        <x:v>46254.4981255671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="484" spans="1:4">
+      <x:c r="A484" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B484" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C484" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D484" s="7">
+        <x:v>46254.49812625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="485" spans="1:4">
+      <x:c r="A485" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B485" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C485" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D485" s="7">
+        <x:v>46254.498127037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="486" spans="1:4">
+      <x:c r="A486" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B486" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C486" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D486" s="7">
+        <x:v>46254.4981277199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="487" spans="1:4">
+      <x:c r="A487" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B487" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C487" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D487" s="7">
+        <x:v>46254.498128588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="488" spans="1:4">
+      <x:c r="A488" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B488" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C488" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D488" s="7">
+        <x:v>46254.4981295949</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="489" spans="1:4">
+      <x:c r="A489" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B489" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C489" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D489" s="7">
+        <x:v>46254.498130625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="490" spans="1:4">
+      <x:c r="A490" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B490" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C490" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D490" s="7">
+        <x:v>46254.4981315625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="491" spans="1:4">
+      <x:c r="A491" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B491" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C491" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D491" s="7">
+        <x:v>46254.4981326273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="492" spans="1:4">
+      <x:c r="A492" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B492" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C492" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D492" s="7">
+        <x:v>46254.4981335648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="493" spans="1:4">
+      <x:c r="A493" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B493" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C493" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D493" s="7">
+        <x:v>46254.4981346412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="494" spans="1:4">
+      <x:c r="A494" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B494" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C494" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D494" s="7">
+        <x:v>46254.4981356713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="495" spans="1:4">
+      <x:c r="A495" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B495" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C495" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D495" s="7">
+        <x:v>46254.4981366204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="496" spans="1:4">
+      <x:c r="A496" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B496" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C496" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D496" s="7">
+        <x:v>46254.4981376736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="497" spans="1:4">
+      <x:c r="A497" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B497" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C497" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D497" s="7">
+        <x:v>46254.4981386458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="498" spans="1:4">
+      <x:c r="A498" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B498" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C498" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D498" s="7">
+        <x:v>46254.4981398032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="499" spans="1:4">
+      <x:c r="A499" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B499" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C499" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D499" s="7">
+        <x:v>46254.4981405787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="500" spans="1:4">
+      <x:c r="A500" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B500" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C500" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D500" s="7">
+        <x:v>46254.4981412384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="501" spans="1:4">
+      <x:c r="A501" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B501" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C501" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D501" s="7">
+        <x:v>46254.4981419329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="502" spans="1:4">
+      <x:c r="A502" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B502" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C502" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D502" s="7">
+        <x:v>46254.4981430093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="503" spans="1:4">
+      <x:c r="A503" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B503" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C503" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D503" s="7">
+        <x:v>46254.4981441319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="504" spans="1:4">
+      <x:c r="A504" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B504" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C504" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D504" s="7">
+        <x:v>46254.4981452315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="505" spans="1:4">
+      <x:c r="A505" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B505" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C505" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D505" s="7">
+        <x:v>46254.4981459144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="506" spans="1:4">
+      <x:c r="A506" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B506" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C506" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D506" s="7">
+        <x:v>46254.4981467477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="507" spans="1:4">
+      <x:c r="A507" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B507" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C507" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D507" s="7">
+        <x:v>46254.4981478472</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="508" spans="1:4">
+      <x:c r="A508" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B508" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C508" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D508" s="7">
+        <x:v>46254.4981487847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="509" spans="1:4">
+      <x:c r="A509" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B509" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C509" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D509" s="7">
+        <x:v>46254.498149838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="510" spans="1:4">
+      <x:c r="A510" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B510" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C510" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D510" s="7">
+        <x:v>46254.4981509722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="511" spans="1:4">
+      <x:c r="A511" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B511" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C511" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D511" s="7">
+        <x:v>46254.498152037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="512" spans="1:4">
+      <x:c r="A512" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B512" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C512" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D512" s="7">
+        <x:v>46254.498153044</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="513" spans="1:4">
+      <x:c r="A513" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B513" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C513" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D513" s="7">
+        <x:v>46254.4981539931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="514" spans="1:4">
+      <x:c r="A514" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B514" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C514" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D514" s="7">
+        <x:v>46254.4981546065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="515" spans="1:4">
+      <x:c r="A515" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B515" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C515" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D515" s="7">
+        <x:v>46254.498155463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="516" spans="1:4">
+      <x:c r="A516" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B516" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C516" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D516" s="7">
+        <x:v>46254.4981561111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="517" spans="1:4">
+      <x:c r="A517" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B517" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C517" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D517" s="7">
+        <x:v>46254.4981571296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="518" spans="1:4">
+      <x:c r="A518" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B518" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C518" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D518" s="7">
+        <x:v>46254.4981583333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="519" spans="1:4">
+      <x:c r="A519" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B519" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C519" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D519" s="7">
+        <x:v>46254.498159375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="520" spans="1:4">
+      <x:c r="A520" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B520" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C520" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D520" s="7">
+        <x:v>46254.4981605208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="521" spans="1:4">
+      <x:c r="A521" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B521" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C521" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D521" s="7">
+        <x:v>46254.4981616204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="522" spans="1:4">
+      <x:c r="A522" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B522" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C522" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D522" s="7">
+        <x:v>46254.499069838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="523" spans="1:4">
+      <x:c r="A523" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B523" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C523" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D523" s="7">
+        <x:v>46254.4990708912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="524" spans="1:4">
+      <x:c r="A524" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B524" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C524" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D524" s="7">
+        <x:v>46254.4990723727</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="525" spans="1:4">
+      <x:c r="A525" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B525" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C525" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D525" s="7">
+        <x:v>46254.4990735185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="526" spans="1:4">
+      <x:c r="A526" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B526" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C526" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D526" s="7">
+        <x:v>46254.4990750579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="527" spans="1:4">
+      <x:c r="A527" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B527" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C527" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D527" s="7">
+        <x:v>46254.4990766551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="528" spans="1:4">
+      <x:c r="A528" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B528" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C528" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D528" s="7">
+        <x:v>46254.4990779861</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="529" spans="1:4">
+      <x:c r="A529" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B529" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C529" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D529" s="7">
+        <x:v>46254.4990792361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="530" spans="1:4">
+      <x:c r="A530" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B530" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C530" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D530" s="7">
+        <x:v>46254.4990804051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="531" spans="1:4">
+      <x:c r="A531" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B531" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C531" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D531" s="7">
+        <x:v>46254.4990819097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="532" spans="1:4">
+      <x:c r="A532" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B532" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C532" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D532" s="7">
+        <x:v>46254.4990828472</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="533" spans="1:4">
+      <x:c r="A533" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B533" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C533" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D533" s="7">
+        <x:v>46254.499083588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="534" spans="1:4">
+      <x:c r="A534" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B534" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C534" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D534" s="7">
+        <x:v>46254.4990844907</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="535" spans="1:4">
+      <x:c r="A535" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B535" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C535" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D535" s="7">
+        <x:v>46254.4990855556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="536" spans="1:4">
+      <x:c r="A536" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B536" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C536" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D536" s="7">
+        <x:v>46254.4990869444</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="537" spans="1:4">
+      <x:c r="A537" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B537" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C537" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D537" s="7">
+        <x:v>46254.4990883449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="538" spans="1:4">
+      <x:c r="A538" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B538" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C538" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D538" s="7">
+        <x:v>46254.4990895255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="539" spans="1:4">
+      <x:c r="A539" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B539" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C539" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D539" s="7">
+        <x:v>46254.499090544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="540" spans="1:4">
+      <x:c r="A540" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B540" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C540" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D540" s="7">
+        <x:v>46254.4990914583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="541" spans="1:4">
+      <x:c r="A541" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B541" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C541" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D541" s="7">
+        <x:v>46254.4990928356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="542" spans="1:4">
+      <x:c r="A542" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B542" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C542" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D542" s="7">
+        <x:v>46254.499093831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="543" spans="1:4">
+      <x:c r="A543" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B543" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C543" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D543" s="7">
+        <x:v>46254.4990950232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="544" spans="1:4">
+      <x:c r="A544" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B544" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C544" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D544" s="7">
+        <x:v>46254.4990961111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="545" spans="1:4">
+      <x:c r="A545" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B545" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C545" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D545" s="7">
+        <x:v>46254.4990972106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="546" spans="1:4">
+      <x:c r="A546" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B546" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C546" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D546" s="7">
+        <x:v>46254.4990979514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="547" spans="1:4">
+      <x:c r="A547" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B547" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C547" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D547" s="7">
+        <x:v>46254.4990987963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="548" spans="1:4">
+      <x:c r="A548" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B548" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C548" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D548" s="7">
+        <x:v>46254.4990997107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="549" spans="1:4">
+      <x:c r="A549" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B549" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C549" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D549" s="7">
+        <x:v>46254.4991007407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="550" spans="1:4">
+      <x:c r="A550" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B550" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C550" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D550" s="7">
+        <x:v>46254.4991021991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="551" spans="1:4">
+      <x:c r="A551" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B551" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C551" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D551" s="7">
+        <x:v>46254.4991033912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="552" spans="1:4">
+      <x:c r="A552" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B552" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C552" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D552" s="7">
+        <x:v>46254.4991046644</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="553" spans="1:4">
+      <x:c r="A553" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B553" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C553" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D553" s="7">
+        <x:v>46254.4991058796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="554" spans="1:4">
+      <x:c r="A554" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B554" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C554" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D554" s="7">
+        <x:v>46254.4991072222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="555" spans="1:4">
+      <x:c r="A555" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B555" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C555" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D555" s="7">
+        <x:v>46254.4991083681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="556" spans="1:4">
+      <x:c r="A556" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B556" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C556" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D556" s="7">
+        <x:v>46254.4991094792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="557" spans="1:4">
+      <x:c r="A557" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B557" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C557" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D557" s="7">
+        <x:v>46254.4991108681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="558" spans="1:4">
+      <x:c r="A558" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B558" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C558" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D558" s="7">
+        <x:v>46254.499111794</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="559" spans="1:4">
+      <x:c r="A559" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B559" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C559" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D559" s="7">
+        <x:v>46254.4991127894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="560" spans="1:4">
+      <x:c r="A560" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B560" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C560" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D560" s="7">
+        <x:v>46254.4991135764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="561" spans="1:4">
+      <x:c r="A561" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B561" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C561" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D561" s="7">
+        <x:v>46254.4991147917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="562" spans="1:4">
+      <x:c r="A562" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B562" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C562" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D562" s="7">
+        <x:v>46254.4991161343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="563" spans="1:4">
+      <x:c r="A563" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B563" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C563" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D563" s="7">
+        <x:v>46254.4991174074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="564" spans="1:4">
+      <x:c r="A564" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B564" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C564" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D564" s="7">
+        <x:v>46254.4991185069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="565" spans="1:4">
+      <x:c r="A565" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B565" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C565" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D565" s="7">
+        <x:v>46254.4991197222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="566" spans="1:4">
+      <x:c r="A566" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B566" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C566" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D566" s="7">
+        <x:v>46254.4991210995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="567" spans="1:4">
+      <x:c r="A567" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B567" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C567" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D567" s="7">
+        <x:v>46254.4991221991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="568" spans="1:4">
+      <x:c r="A568" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B568" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C568" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D568" s="7">
+        <x:v>46254.4991235648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="569" spans="1:4">
+      <x:c r="A569" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B569" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C569" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D569" s="7">
+        <x:v>46254.4991246991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="570" spans="1:4">
+      <x:c r="A570" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B570" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C570" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D570" s="7">
+        <x:v>46254.4991256829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="571" spans="1:4">
+      <x:c r="A571" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B571" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C571" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D571" s="7">
+        <x:v>46254.4991266319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="572" spans="1:4">
+      <x:c r="A572" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B572" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C572" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D572" s="7">
+        <x:v>46254.4991278472</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="573" spans="1:4">
+      <x:c r="A573" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B573" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C573" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D573" s="7">
+        <x:v>46254.4991293982</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="574" spans="1:4">
+      <x:c r="A574" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B574" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C574" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D574" s="7">
+        <x:v>46254.4991305324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="575" spans="1:4">
+      <x:c r="A575" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B575" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C575" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D575" s="7">
+        <x:v>46254.4991319097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="576" spans="1:4">
+      <x:c r="A576" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B576" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C576" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D576" s="7">
+        <x:v>46254.4991330903</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="577" spans="1:4">
+      <x:c r="A577" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B577" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C577" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D577" s="7">
+        <x:v>46254.4991341088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="578" spans="1:4">
+      <x:c r="A578" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B578" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C578" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D578" s="7">
+        <x:v>46254.4991353935</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="579" spans="1:4">
+      <x:c r="A579" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B579" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C579" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D579" s="7">
+        <x:v>46254.4991364468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="580" spans="1:4">
+      <x:c r="A580" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B580" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C580" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D580" s="7">
+        <x:v>46254.4991379398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="581" spans="1:4">
+      <x:c r="A581" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B581" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C581" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D581" s="7">
+        <x:v>46254.4991390856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="582" spans="1:4">
+      <x:c r="A582" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B582" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C582" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D582" s="7">
+        <x:v>46254.4991397338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="583" spans="1:4">
+      <x:c r="A583" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B583" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C583" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D583" s="7">
+        <x:v>46254.4991405787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="584" spans="1:4">
+      <x:c r="A584" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B584" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C584" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D584" s="7">
+        <x:v>46254.4991413889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="585" spans="1:4">
+      <x:c r="A585" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B585" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C585" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D585" s="7">
+        <x:v>46254.4991424537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="586" spans="1:4">
+      <x:c r="A586" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B586" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C586" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D586" s="7">
+        <x:v>46254.4991437384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="587" spans="1:4">
+      <x:c r="A587" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B587" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C587" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D587" s="7">
+        <x:v>46254.499145162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="588" spans="1:4">
+      <x:c r="A588" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B588" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C588" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D588" s="7">
+        <x:v>46254.4991462384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="589" spans="1:4">
+      <x:c r="A589" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B589" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C589" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D589" s="7">
+        <x:v>46254.499147662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="590" spans="1:4">
+      <x:c r="A590" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B590" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C590" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D590" s="7">
+        <x:v>46254.4991488657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="591" spans="1:4">
+      <x:c r="A591" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B591" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C591" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D591" s="7">
+        <x:v>46254.4991501852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="592" spans="1:4">
+      <x:c r="A592" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B592" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C592" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D592" s="7">
+        <x:v>46254.4991511921</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="593" spans="1:4">
+      <x:c r="A593" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B593" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C593" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D593" s="7">
+        <x:v>46254.4991526736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="594" spans="1:4">
+      <x:c r="A594" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B594" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C594" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D594" s="7">
+        <x:v>46254.4991537384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="595" spans="1:4">
+      <x:c r="A595" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B595" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C595" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D595" s="7">
+        <x:v>46254.4991546065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="596" spans="1:4">
+      <x:c r="A596" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B596" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C596" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D596" s="7">
+        <x:v>46254.4991554282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="597" spans="1:4">
+      <x:c r="A597" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B597" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C597" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D597" s="7">
+        <x:v>46254.4991564583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="598" spans="1:4">
+      <x:c r="A598" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B598" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C598" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D598" s="7">
+        <x:v>46254.4991577662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="599" spans="1:4">
+      <x:c r="A599" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B599" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C599" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D599" s="7">
+        <x:v>46254.4991591667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="600" spans="1:4">
+      <x:c r="A600" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B600" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C600" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D600" s="7">
+        <x:v>46254.4991604051</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="601" spans="1:4">
+      <x:c r="A601" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B601" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C601" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D601" s="7">
+        <x:v>46254.4991615046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="602" spans="1:4">
+      <x:c r="A602" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B602" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C602" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D602" s="7">
+        <x:v>46254.4991629398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="603" spans="1:4">
+      <x:c r="A603" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B603" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C603" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D603" s="7">
+        <x:v>46254.4991641667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="604" spans="1:4">
+      <x:c r="A604" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B604" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C604" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D604" s="7">
+        <x:v>46254.4991657407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="605" spans="1:4">
+      <x:c r="A605" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B605" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C605" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D605" s="7">
+        <x:v>46254.4991669792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="606" spans="1:4">
+      <x:c r="A606" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B606" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C606" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D606" s="7">
+        <x:v>46254.4991683102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="607" spans="1:4">
+      <x:c r="A607" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B607" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C607" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D607" s="7">
+        <x:v>46254.4991692477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="608" spans="1:4">
+      <x:c r="A608" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B608" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C608" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D608" s="7">
+        <x:v>46254.4991701852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="609" spans="1:4">
+      <x:c r="A609" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B609" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C609" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D609" s="7">
+        <x:v>46254.4991712269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="610" spans="1:4">
+      <x:c r="A610" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B610" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C610" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D610" s="7">
+        <x:v>46254.4991723495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="611" spans="1:4">
+      <x:c r="A611" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B611" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C611" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D611" s="7">
+        <x:v>46254.4991740509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="612" spans="1:4">
+      <x:c r="A612" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B612" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C612" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D612" s="7">
+        <x:v>46254.4991752662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="613" spans="1:4">
+      <x:c r="A613" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B613" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C613" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D613" s="7">
+        <x:v>46254.4991767477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="614" spans="1:4">
+      <x:c r="A614" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B614" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C614" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D614" s="7">
+        <x:v>46254.4991782986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="615" spans="1:4">
+      <x:c r="A615" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B615" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C615" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D615" s="7">
+        <x:v>46254.4991796296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="616" spans="1:4">
+      <x:c r="A616" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B616" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C616" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D616" s="7">
+        <x:v>46254.4991811111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="617" spans="1:4">
+      <x:c r="A617" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B617" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C617" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D617" s="7">
+        <x:v>46254.4991822917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="618" spans="1:4">
+      <x:c r="A618" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B618" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C618" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D618" s="7">
+        <x:v>46254.499183287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="619" spans="1:4">
+      <x:c r="A619" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B619" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C619" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D619" s="7">
+        <x:v>46254.499184294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="620" spans="1:4">
+      <x:c r="A620" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B620" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C620" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D620" s="7">
+        <x:v>46254.4991851389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="621" spans="1:4">
+      <x:c r="A621" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B621" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C621" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D621" s="7">
+        <x:v>46254.4991862153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="622" spans="1:4">
+      <x:c r="A622" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B622" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C622" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D622" s="7">
+        <x:v>46254.5001876505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="623" spans="1:4">
+      <x:c r="A623" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B623" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C623" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D623" s="7">
+        <x:v>46254.5001889815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="624" spans="1:4">
+      <x:c r="A624" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B624" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C624" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D624" s="7">
+        <x:v>46254.5001903356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="625" spans="1:4">
+      <x:c r="A625" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B625" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C625" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D625" s="7">
+        <x:v>46254.5001914352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="626" spans="1:4">
+      <x:c r="A626" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B626" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C626" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D626" s="7">
+        <x:v>46254.5001926736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="627" spans="1:4">
+      <x:c r="A627" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B627" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C627" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D627" s="7">
+        <x:v>46254.5001940509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="628" spans="1:4">
+      <x:c r="A628" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B628" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C628" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D628" s="7">
+        <x:v>46254.5001951505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="629" spans="1:4">
+      <x:c r="A629" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B629" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C629" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D629" s="7">
+        <x:v>46254.5001959606</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="630" spans="1:4">
+      <x:c r="A630" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B630" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C630" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D630" s="7">
+        <x:v>46254.5001968287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="631" spans="1:4">
+      <x:c r="A631" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B631" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C631" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D631" s="7">
+        <x:v>46254.5001977431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="632" spans="1:4">
+      <x:c r="A632" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B632" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C632" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D632" s="7">
+        <x:v>46254.5001989583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="633" spans="1:4">
+      <x:c r="A633" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B633" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C633" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D633" s="7">
+        <x:v>46254.5002003935</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="634" spans="1:4">
+      <x:c r="A634" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B634" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C634" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D634" s="7">
+        <x:v>46254.5002017593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="635" spans="1:4">
+      <x:c r="A635" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B635" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C635" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D635" s="7">
+        <x:v>46254.5002029861</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="636" spans="1:4">
+      <x:c r="A636" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B636" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C636" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D636" s="7">
+        <x:v>46254.5002041782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="637" spans="1:4">
+      <x:c r="A637" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B637" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C637" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D637" s="7">
+        <x:v>46254.500205544</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="638" spans="1:4">
+      <x:c r="A638" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B638" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C638" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D638" s="7">
+        <x:v>46254.5002066551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="639" spans="1:4">
+      <x:c r="A639" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B639" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C639" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D639" s="7">
+        <x:v>46254.5002077431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="640" spans="1:4">
+      <x:c r="A640" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B640" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C640" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D640" s="7">
+        <x:v>46254.5002086574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="641" spans="1:4">
+      <x:c r="A641" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B641" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C641" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D641" s="7">
+        <x:v>46254.5002096759</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="642" spans="1:4">
+      <x:c r="A642" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B642" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C642" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D642" s="7">
+        <x:v>46254.5002104282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="643" spans="1:4">
+      <x:c r="A643" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B643" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C643" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D643" s="7">
+        <x:v>46254.5002112847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="644" spans="1:4">
+      <x:c r="A644" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B644" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C644" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D644" s="7">
+        <x:v>46254.5002122801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="645" spans="1:4">
+      <x:c r="A645" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B645" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C645" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D645" s="7">
+        <x:v>46254.5002137731</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="646" spans="1:4">
+      <x:c r="A646" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B646" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C646" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D646" s="7">
+        <x:v>46254.5002150116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="647" spans="1:4">
+      <x:c r="A647" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B647" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C647" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D647" s="7">
+        <x:v>46254.500216088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="648" spans="1:4">
+      <x:c r="A648" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B648" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C648" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D648" s="7">
+        <x:v>46254.5002176505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="649" spans="1:4">
+      <x:c r="A649" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B649" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C649" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D649" s="7">
+        <x:v>46254.5002189815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="650" spans="1:4">
+      <x:c r="A650" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B650" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C650" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D650" s="7">
+        <x:v>46254.5002203009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="651" spans="1:4">
+      <x:c r="A651" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B651" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C651" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D651" s="7">
+        <x:v>46254.5002213657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="652" spans="1:4">
+      <x:c r="A652" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B652" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C652" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D652" s="7">
+        <x:v>46254.5002228819</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="653" spans="1:4">
+      <x:c r="A653" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B653" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C653" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D653" s="7">
+        <x:v>46254.5002240046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="654" spans="1:4">
+      <x:c r="A654" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B654" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C654" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D654" s="7">
+        <x:v>46254.5002249074</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="655" spans="1:4">
+      <x:c r="A655" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B655" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C655" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D655" s="7">
+        <x:v>46254.5002257292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="656" spans="1:4">
+      <x:c r="A656" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B656" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C656" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D656" s="7">
+        <x:v>46254.5002268981</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="657" spans="1:4">
+      <x:c r="A657" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B657" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C657" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D657" s="7">
+        <x:v>46254.5002284491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="658" spans="1:4">
+      <x:c r="A658" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B658" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C658" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D658" s="7">
+        <x:v>46254.5002295602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="659" spans="1:4">
+      <x:c r="A659" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B659" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C659" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D659" s="7">
+        <x:v>46254.5002310069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="660" spans="1:4">
+      <x:c r="A660" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B660" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C660" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D660" s="7">
+        <x:v>46254.5002325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="661" spans="1:4">
+      <x:c r="A661" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B661" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C661" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D661" s="7">
+        <x:v>46254.5002338426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="662" spans="1:4">
+      <x:c r="A662" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B662" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C662" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D662" s="7">
+        <x:v>46254.5002351968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="663" spans="1:4">
+      <x:c r="A663" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B663" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C663" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D663" s="7">
+        <x:v>46254.5002366667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="664" spans="1:4">
+      <x:c r="A664" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B664" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C664" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D664" s="7">
+        <x:v>46254.5002380787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="665" spans="1:4">
+      <x:c r="A665" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B665" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C665" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D665" s="7">
+        <x:v>46254.5002389468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="666" spans="1:4">
+      <x:c r="A666" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B666" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C666" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D666" s="7">
+        <x:v>46254.5002397917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="667" spans="1:4">
+      <x:c r="A667" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B667" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C667" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D667" s="7">
+        <x:v>46254.5002407176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="668" spans="1:4">
+      <x:c r="A668" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B668" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C668" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D668" s="7">
+        <x:v>46254.5002421181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="669" spans="1:4">
+      <x:c r="A669" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B669" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C669" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D669" s="7">
+        <x:v>46254.5002435417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="670" spans="1:4">
+      <x:c r="A670" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B670" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C670" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D670" s="7">
+        <x:v>46254.5002449769</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="671" spans="1:4">
+      <x:c r="A671" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B671" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C671" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D671" s="7">
+        <x:v>46254.5002464236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="672" spans="1:4">
+      <x:c r="A672" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B672" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C672" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D672" s="7">
+        <x:v>46254.5002480093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="673" spans="1:4">
+      <x:c r="A673" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B673" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C673" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D673" s="7">
+        <x:v>46254.5002495833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="674" spans="1:4">
+      <x:c r="A674" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B674" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C674" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D674" s="7">
+        <x:v>46254.5002509028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="675" spans="1:4">
+      <x:c r="A675" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B675" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C675" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D675" s="7">
+        <x:v>46254.5002522917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="676" spans="1:4">
+      <x:c r="A676" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B676" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C676" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D676" s="7">
+        <x:v>46254.5002532639</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="677" spans="1:4">
+      <x:c r="A677" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B677" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C677" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D677" s="7">
+        <x:v>46254.5002542593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="678" spans="1:4">
+      <x:c r="A678" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B678" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C678" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D678" s="7">
+        <x:v>46254.5002551852</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="679" spans="1:4">
+      <x:c r="A679" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B679" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C679" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D679" s="7">
+        <x:v>46254.5002560185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="680" spans="1:4">
+      <x:c r="A680" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B680" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C680" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D680" s="7">
+        <x:v>46254.5002571875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="681" spans="1:4">
+      <x:c r="A681" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B681" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C681" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D681" s="7">
+        <x:v>46254.5002584259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="682" spans="1:4">
+      <x:c r="A682" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B682" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C682" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D682" s="7">
+        <x:v>46254.5002596412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="683" spans="1:4">
+      <x:c r="A683" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B683" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C683" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D683" s="7">
+        <x:v>46254.5002610069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="684" spans="1:4">
+      <x:c r="A684" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B684" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C684" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D684" s="7">
+        <x:v>46254.5002623032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="685" spans="1:4">
+      <x:c r="A685" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B685" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C685" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D685" s="7">
+        <x:v>46254.5002637384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="686" spans="1:4">
+      <x:c r="A686" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B686" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C686" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D686" s="7">
+        <x:v>46254.5002648495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="687" spans="1:4">
+      <x:c r="A687" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B687" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C687" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D687" s="7">
+        <x:v>46254.5002658912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="688" spans="1:4">
+      <x:c r="A688" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B688" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C688" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D688" s="7">
+        <x:v>46254.5002671991</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="689" spans="1:4">
+      <x:c r="A689" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B689" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C689" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D689" s="7">
+        <x:v>46254.5002683681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="690" spans="1:4">
+      <x:c r="A690" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B690" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C690" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D690" s="7">
+        <x:v>46254.5002695139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="691" spans="1:4">
+      <x:c r="A691" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B691" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C691" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D691" s="7">
+        <x:v>46254.5002707407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="692" spans="1:4">
+      <x:c r="A692" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B692" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C692" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D692" s="7">
+        <x:v>46254.5002721759</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="693" spans="1:4">
+      <x:c r="A693" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B693" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C693" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D693" s="7">
+        <x:v>46254.5002739468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="694" spans="1:4">
+      <x:c r="A694" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B694" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C694" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D694" s="7">
+        <x:v>46254.500275463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="695" spans="1:4">
+      <x:c r="A695" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B695" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C695" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D695" s="7">
+        <x:v>46254.5002774306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="696" spans="1:4">
+      <x:c r="A696" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B696" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C696" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D696" s="7">
+        <x:v>46254.5002797569</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="697" spans="1:4">
+      <x:c r="A697" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B697" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C697" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D697" s="7">
+        <x:v>46254.5002819792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="698" spans="1:4">
+      <x:c r="A698" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B698" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C698" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D698" s="7">
+        <x:v>46254.500283669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="699" spans="1:4">
+      <x:c r="A699" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B699" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C699" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D699" s="7">
+        <x:v>46254.5002855324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="700" spans="1:4">
+      <x:c r="A700" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B700" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C700" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D700" s="7">
+        <x:v>46254.5002878009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="701" spans="1:4">
+      <x:c r="A701" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B701" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C701" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D701" s="7">
+        <x:v>46254.5002897454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="702" spans="1:4">
+      <x:c r="A702" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B702" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C702" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D702" s="7">
+        <x:v>46254.5002918171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="703" spans="1:4">
+      <x:c r="A703" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B703" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C703" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D703" s="7">
+        <x:v>46254.5002935995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="704" spans="1:4">
+      <x:c r="A704" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B704" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C704" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D704" s="7">
+        <x:v>46254.5002955556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="705" spans="1:4">
+      <x:c r="A705" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B705" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C705" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D705" s="7">
+        <x:v>46254.5002973958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="706" spans="1:4">
+      <x:c r="A706" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B706" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C706" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D706" s="7">
+        <x:v>46254.5002990394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="707" spans="1:4">
+      <x:c r="A707" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B707" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C707" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D707" s="7">
+        <x:v>46254.5003011227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="708" spans="1:4">
+      <x:c r="A708" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B708" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C708" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D708" s="7">
+        <x:v>46254.5003023958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="709" spans="1:4">
+      <x:c r="A709" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B709" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C709" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D709" s="7">
+        <x:v>46254.5003036458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="710" spans="1:4">
+      <x:c r="A710" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B710" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C710" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D710" s="7">
+        <x:v>46254.5003048958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="711" spans="1:4">
+      <x:c r="A711" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B711" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C711" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D711" s="7">
+        <x:v>46254.5003061458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="712" spans="1:4">
+      <x:c r="A712" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B712" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C712" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D712" s="7">
+        <x:v>46254.5003073843</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="713" spans="1:4">
+      <x:c r="A713" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B713" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C713" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D713" s="7">
+        <x:v>46254.500308588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="714" spans="1:4">
+      <x:c r="A714" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B714" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C714" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D714" s="7">
+        <x:v>46254.500309838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="715" spans="1:4">
+      <x:c r="A715" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B715" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C715" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D715" s="7">
+        <x:v>46254.5003111227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="716" spans="1:4">
+      <x:c r="A716" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B716" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C716" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D716" s="7">
+        <x:v>46254.5003122685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="717" spans="1:4">
+      <x:c r="A717" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B717" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C717" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D717" s="7">
+        <x:v>46254.5003134722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="718" spans="1:4">
+      <x:c r="A718" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B718" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C718" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D718" s="7">
+        <x:v>46254.500314838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="719" spans="1:4">
+      <x:c r="A719" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B719" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C719" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D719" s="7">
+        <x:v>46254.5003162963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="720" spans="1:4">
+      <x:c r="A720" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B720" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C720" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D720" s="7">
+        <x:v>46254.5003177894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="721" spans="1:4">
+      <x:c r="A721" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B721" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C721" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D721" s="7">
+        <x:v>46254.5003191898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="722" spans="1:4">
+      <x:c r="A722" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B722" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C722" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D722" s="7">
+        <x:v>46254.5009567245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="723" spans="1:4">
+      <x:c r="A723" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B723" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C723" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D723" s="7">
+        <x:v>46254.5009588889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="724" spans="1:4">
+      <x:c r="A724" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B724" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C724" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D724" s="7">
+        <x:v>46254.5009610764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="725" spans="1:4">
+      <x:c r="A725" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B725" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C725" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D725" s="7">
+        <x:v>46254.5009630787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="726" spans="1:4">
+      <x:c r="A726" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B726" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C726" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D726" s="7">
+        <x:v>46254.5009653935</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="727" spans="1:4">
+      <x:c r="A727" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B727" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C727" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D727" s="7">
+        <x:v>46254.5009672917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="728" spans="1:4">
+      <x:c r="A728" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B728" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C728" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D728" s="7">
+        <x:v>46254.5009692245</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="729" spans="1:4">
+      <x:c r="A729" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B729" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C729" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D729" s="7">
+        <x:v>46254.5009711806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="730" spans="1:4">
+      <x:c r="A730" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B730" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C730" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D730" s="7">
+        <x:v>46254.5009730556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="731" spans="1:4">
+      <x:c r="A731" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B731" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C731" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D731" s="7">
+        <x:v>46254.5009751157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="732" spans="1:4">
+      <x:c r="A732" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B732" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C732" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D732" s="7">
+        <x:v>46254.5009768056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="733" spans="1:4">
+      <x:c r="A733" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B733" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C733" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D733" s="7">
+        <x:v>46254.5009789352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="734" spans="1:4">
+      <x:c r="A734" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B734" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C734" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D734" s="7">
+        <x:v>46254.5009811343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="735" spans="1:4">
+      <x:c r="A735" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B735" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C735" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D735" s="7">
+        <x:v>46254.500983125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="736" spans="1:4">
+      <x:c r="A736" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B736" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C736" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D736" s="7">
+        <x:v>46254.5009849653</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="737" spans="1:4">
+      <x:c r="A737" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B737" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C737" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D737" s="7">
+        <x:v>46254.5009869792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="738" spans="1:4">
+      <x:c r="A738" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B738" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C738" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D738" s="7">
+        <x:v>46254.5009892361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="739" spans="1:4">
+      <x:c r="A739" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B739" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C739" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D739" s="7">
+        <x:v>46254.50099125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="740" spans="1:4">
+      <x:c r="A740" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B740" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C740" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D740" s="7">
+        <x:v>46254.5009930556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="741" spans="1:4">
+      <x:c r="A741" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B741" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C741" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D741" s="7">
+        <x:v>46254.5009947917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="742" spans="1:4">
+      <x:c r="A742" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B742" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C742" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D742" s="7">
+        <x:v>46254.5009964815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="743" spans="1:4">
+      <x:c r="A743" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B743" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C743" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D743" s="7">
+        <x:v>46254.5009987037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="744" spans="1:4">
+      <x:c r="A744" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B744" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C744" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D744" s="7">
+        <x:v>46254.5010010532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="745" spans="1:4">
+      <x:c r="A745" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B745" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C745" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D745" s="7">
+        <x:v>46254.5010033449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="746" spans="1:4">
+      <x:c r="A746" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B746" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C746" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D746" s="7">
+        <x:v>46254.5010055093</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="747" spans="1:4">
+      <x:c r="A747" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B747" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C747" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D747" s="7">
+        <x:v>46254.5010076968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="748" spans="1:4">
+      <x:c r="A748" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B748" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C748" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D748" s="7">
+        <x:v>46254.5010098495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="749" spans="1:4">
+      <x:c r="A749" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B749" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C749" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D749" s="7">
+        <x:v>46254.5010119329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="750" spans="1:4">
+      <x:c r="A750" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B750" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C750" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D750" s="7">
+        <x:v>46254.5010142477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="751" spans="1:4">
+      <x:c r="A751" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B751" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C751" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D751" s="7">
+        <x:v>46254.501016088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="752" spans="1:4">
+      <x:c r="A752" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B752" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C752" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D752" s="7">
+        <x:v>46254.5010182755</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="753" spans="1:4">
+      <x:c r="A753" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B753" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C753" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D753" s="7">
+        <x:v>46254.501020463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="754" spans="1:4">
+      <x:c r="A754" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B754" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C754" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D754" s="7">
+        <x:v>46254.501022662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="755" spans="1:4">
+      <x:c r="A755" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B755" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C755" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D755" s="7">
+        <x:v>46254.5010248843</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="756" spans="1:4">
+      <x:c r="A756" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B756" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C756" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D756" s="7">
+        <x:v>46254.5010268634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="757" spans="1:4">
+      <x:c r="A757" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B757" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C757" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D757" s="7">
+        <x:v>46254.5010290046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="758" spans="1:4">
+      <x:c r="A758" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B758" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C758" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D758" s="7">
+        <x:v>46254.5010308912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="759" spans="1:4">
+      <x:c r="A759" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B759" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C759" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D759" s="7">
+        <x:v>46254.5010327431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="760" spans="1:4">
+      <x:c r="A760" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B760" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C760" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D760" s="7">
+        <x:v>46254.5010344213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="761" spans="1:4">
+      <x:c r="A761" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B761" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C761" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D761" s="7">
+        <x:v>46254.5010363079</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="762" spans="1:4">
+      <x:c r="A762" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B762" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C762" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D762" s="7">
+        <x:v>46254.501038588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="763" spans="1:4">
+      <x:c r="A763" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B763" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C763" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D763" s="7">
+        <x:v>46254.5010409491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="764" spans="1:4">
+      <x:c r="A764" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B764" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C764" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D764" s="7">
+        <x:v>46254.5010429977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="765" spans="1:4">
+      <x:c r="A765" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B765" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C765" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D765" s="7">
+        <x:v>46254.501045</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="766" spans="1:4">
+      <x:c r="A766" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B766" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C766" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D766" s="7">
+        <x:v>46254.5010472801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="767" spans="1:4">
+      <x:c r="A767" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B767" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C767" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D767" s="7">
+        <x:v>46254.5010492014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="768" spans="1:4">
+      <x:c r="A768" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B768" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C768" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D768" s="7">
+        <x:v>46254.5010510764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="769" spans="1:4">
+      <x:c r="A769" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B769" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C769" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D769" s="7">
+        <x:v>46254.5010531829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="770" spans="1:4">
+      <x:c r="A770" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B770" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C770" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D770" s="7">
+        <x:v>46254.5010552894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="771" spans="1:4">
+      <x:c r="A771" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B771" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C771" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D771" s="7">
+        <x:v>46254.5010573495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="772" spans="1:4">
+      <x:c r="A772" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B772" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C772" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D772" s="7">
+        <x:v>46254.5010597917</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="773" spans="1:4">
+      <x:c r="A773" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B773" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C773" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D773" s="7">
+        <x:v>46254.5010622801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="774" spans="1:4">
+      <x:c r="A774" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B774" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C774" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D774" s="7">
+        <x:v>46254.5010643982</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="775" spans="1:4">
+      <x:c r="A775" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B775" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C775" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D775" s="7">
+        <x:v>46254.5010665393</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="776" spans="1:4">
+      <x:c r="A776" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B776" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C776" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D776" s="7">
+        <x:v>46254.5010681829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="777" spans="1:4">
+      <x:c r="A777" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B777" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C777" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D777" s="7">
+        <x:v>46254.5010695602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="778" spans="1:4">
+      <x:c r="A778" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B778" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C778" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D778" s="7">
+        <x:v>46254.5010706829</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="779" spans="1:4">
+      <x:c r="A779" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B779" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C779" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D779" s="7">
+        <x:v>46254.5010718403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="780" spans="1:4">
+      <x:c r="A780" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B780" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C780" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D780" s="7">
+        <x:v>46254.5010730556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="781" spans="1:4">
+      <x:c r="A781" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B781" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C781" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D781" s="7">
+        <x:v>46254.5010743171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="782" spans="1:4">
+      <x:c r="A782" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B782" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C782" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D782" s="7">
+        <x:v>46254.5010756713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="783" spans="1:4">
+      <x:c r="A783" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B783" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C783" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D783" s="7">
+        <x:v>46254.5010775347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="784" spans="1:4">
+      <x:c r="A784" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B784" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C784" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D784" s="7">
+        <x:v>46254.5010795023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="785" spans="1:4">
+      <x:c r="A785" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B785" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C785" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D785" s="7">
+        <x:v>46254.5010813194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="786" spans="1:4">
+      <x:c r="A786" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B786" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C786" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D786" s="7">
+        <x:v>46254.5010834607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="787" spans="1:4">
+      <x:c r="A787" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B787" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C787" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D787" s="7">
+        <x:v>46254.5010848843</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="788" spans="1:4">
+      <x:c r="A788" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B788" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C788" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D788" s="7">
+        <x:v>46254.5010864005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="789" spans="1:4">
+      <x:c r="A789" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B789" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C789" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D789" s="7">
+        <x:v>46254.5010893634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="790" spans="1:4">
+      <x:c r="A790" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B790" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C790" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D790" s="7">
+        <x:v>46254.5010934144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="791" spans="1:4">
+      <x:c r="A791" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B791" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C791" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D791" s="7">
+        <x:v>46254.5010955208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="792" spans="1:4">
+      <x:c r="A792" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B792" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C792" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D792" s="7">
+        <x:v>46254.5011020255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="793" spans="1:4">
+      <x:c r="A793" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B793" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C793" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D793" s="7">
+        <x:v>46254.50110375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="794" spans="1:4">
+      <x:c r="A794" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B794" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C794" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D794" s="7">
+        <x:v>46254.5011051389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="795" spans="1:4">
+      <x:c r="A795" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B795" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C795" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D795" s="7">
+        <x:v>46254.5011065856</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="796" spans="1:4">
+      <x:c r="A796" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B796" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C796" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D796" s="7">
+        <x:v>46254.5011079977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="797" spans="1:4">
+      <x:c r="A797" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B797" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C797" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D797" s="7">
+        <x:v>46254.5011092824</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="798" spans="1:4">
+      <x:c r="A798" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B798" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C798" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D798" s="7">
+        <x:v>46254.5011107407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="799" spans="1:4">
+      <x:c r="A799" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B799" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C799" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D799" s="7">
+        <x:v>46254.5011121412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="800" spans="1:4">
+      <x:c r="A800" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B800" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C800" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D800" s="7">
+        <x:v>46254.5011135185</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="801" spans="1:4">
+      <x:c r="A801" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B801" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C801" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D801" s="7">
+        <x:v>46254.5011154398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="802" spans="1:4">
+      <x:c r="A802" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B802" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C802" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D802" s="7">
+        <x:v>46254.5011168056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="803" spans="1:4">
+      <x:c r="A803" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B803" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C803" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D803" s="7">
+        <x:v>46254.5011181597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="804" spans="1:4">
+      <x:c r="A804" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B804" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C804" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D804" s="7">
+        <x:v>46254.5011196181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="805" spans="1:4">
+      <x:c r="A805" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B805" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C805" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D805" s="7">
+        <x:v>46254.5011210532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="806" spans="1:4">
+      <x:c r="A806" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B806" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C806" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D806" s="7">
+        <x:v>46254.5011225347</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="807" spans="1:4">
+      <x:c r="A807" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B807" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C807" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D807" s="7">
+        <x:v>46254.5011238889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="808" spans="1:4">
+      <x:c r="A808" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B808" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C808" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D808" s="7">
+        <x:v>46254.5011254398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="809" spans="1:4">
+      <x:c r="A809" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B809" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C809" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D809" s="7">
+        <x:v>46254.5011269907</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="810" spans="1:4">
+      <x:c r="A810" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B810" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C810" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D810" s="7">
+        <x:v>46254.5011286574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="811" spans="1:4">
+      <x:c r="A811" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B811" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C811" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D811" s="7">
+        <x:v>46254.5011301042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="812" spans="1:4">
+      <x:c r="A812" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B812" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C812" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D812" s="7">
+        <x:v>46254.5011315741</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="813" spans="1:4">
+      <x:c r="A813" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B813" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C813" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D813" s="7">
+        <x:v>46254.5011331366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="814" spans="1:4">
+      <x:c r="A814" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B814" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C814" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D814" s="7">
+        <x:v>46254.5011344907</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="815" spans="1:4">
+      <x:c r="A815" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B815" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C815" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D815" s="7">
+        <x:v>46254.5011358796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="816" spans="1:4">
+      <x:c r="A816" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B816" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C816" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D816" s="7">
+        <x:v>46254.501137419</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="817" spans="1:4">
+      <x:c r="A817" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B817" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C817" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D817" s="7">
+        <x:v>46254.5011387269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="818" spans="1:4">
+      <x:c r="A818" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B818" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C818" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D818" s="7">
+        <x:v>46254.5011407176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="819" spans="1:4">
+      <x:c r="A819" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B819" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C819" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D819" s="7">
+        <x:v>46254.5011423727</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="820" spans="1:4">
+      <x:c r="A820" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B820" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C820" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D820" s="7">
+        <x:v>46254.5011437153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="821" spans="1:4">
+      <x:c r="A821" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B821" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C821" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D821" s="7">
+        <x:v>46254.5011452431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="822" spans="1:4">
+      <x:c r="A822" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B822" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C822" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D822" s="7">
+        <x:v>46254.5024855208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="823" spans="1:4">
+      <x:c r="A823" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B823" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C823" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D823" s="7">
+        <x:v>46254.5024869792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="824" spans="1:4">
+      <x:c r="A824" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B824" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C824" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D824" s="7">
+        <x:v>46254.5024884375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="825" spans="1:4">
+      <x:c r="A825" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B825" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C825" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D825" s="7">
+        <x:v>46254.5024901042</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="826" spans="1:4">
+      <x:c r="A826" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B826" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C826" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D826" s="7">
+        <x:v>46254.5024916782</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="827" spans="1:4">
+      <x:c r="A827" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B827" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C827" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D827" s="7">
+        <x:v>46254.502493287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="828" spans="1:4">
+      <x:c r="A828" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B828" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C828" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D828" s="7">
+        <x:v>46254.5024947222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="829" spans="1:4">
+      <x:c r="A829" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B829" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C829" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D829" s="7">
+        <x:v>46254.5024962153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="830" spans="1:4">
+      <x:c r="A830" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B830" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C830" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D830" s="7">
+        <x:v>46254.5024978241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="831" spans="1:4">
+      <x:c r="A831" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B831" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C831" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D831" s="7">
+        <x:v>46254.5024990972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="832" spans="1:4">
+      <x:c r="A832" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B832" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C832" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D832" s="7">
+        <x:v>46254.5025005208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="833" spans="1:4">
+      <x:c r="A833" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B833" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C833" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D833" s="7">
+        <x:v>46254.5025023032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="834" spans="1:4">
+      <x:c r="A834" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B834" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C834" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D834" s="7">
+        <x:v>46254.5025037847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="835" spans="1:4">
+      <x:c r="A835" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B835" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C835" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D835" s="7">
+        <x:v>46254.5025052894</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="836" spans="1:4">
+      <x:c r="A836" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B836" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C836" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D836" s="7">
+        <x:v>46254.5025067361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="837" spans="1:4">
+      <x:c r="A837" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B837" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C837" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D837" s="7">
+        <x:v>46254.5025081713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="838" spans="1:4">
+      <x:c r="A838" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B838" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C838" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D838" s="7">
+        <x:v>46254.5025096065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="839" spans="1:4">
+      <x:c r="A839" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B839" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C839" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D839" s="7">
+        <x:v>46254.502511169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="840" spans="1:4">
+      <x:c r="A840" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B840" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C840" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D840" s="7">
+        <x:v>46254.5025126157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="841" spans="1:4">
+      <x:c r="A841" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B841" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C841" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D841" s="7">
+        <x:v>46254.5025140741</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="842" spans="1:4">
+      <x:c r="A842" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B842" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C842" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D842" s="7">
+        <x:v>46254.5025157176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="843" spans="1:4">
+      <x:c r="A843" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B843" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C843" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D843" s="7">
+        <x:v>46254.502517338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="844" spans="1:4">
+      <x:c r="A844" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B844" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C844" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D844" s="7">
+        <x:v>46254.5025188889</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="845" spans="1:4">
+      <x:c r="A845" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B845" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C845" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D845" s="7">
+        <x:v>46254.5025207523</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="846" spans="1:4">
+      <x:c r="A846" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B846" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C846" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D846" s="7">
+        <x:v>46254.5025225463</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="847" spans="1:4">
+      <x:c r="A847" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B847" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C847" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D847" s="7">
+        <x:v>46254.5025242361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="848" spans="1:4">
+      <x:c r="A848" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B848" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C848" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D848" s="7">
+        <x:v>46254.5025255671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="849" spans="1:4">
+      <x:c r="A849" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B849" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C849" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D849" s="7">
+        <x:v>46254.5025268866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="850" spans="1:4">
+      <x:c r="A850" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B850" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C850" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D850" s="7">
+        <x:v>46254.5025285069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="851" spans="1:4">
+      <x:c r="A851" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B851" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C851" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D851" s="7">
+        <x:v>46254.5025300694</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="852" spans="1:4">
+      <x:c r="A852" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B852" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C852" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D852" s="7">
+        <x:v>46254.5025320139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="853" spans="1:4">
+      <x:c r="A853" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B853" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C853" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D853" s="7">
+        <x:v>46254.5025336574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="854" spans="1:4">
+      <x:c r="A854" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B854" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C854" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D854" s="7">
+        <x:v>46254.5025357176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="855" spans="1:4">
+      <x:c r="A855" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B855" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C855" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D855" s="7">
+        <x:v>46254.5025384722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="856" spans="1:4">
+      <x:c r="A856" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B856" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C856" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D856" s="7">
+        <x:v>46254.5025416204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="857" spans="1:4">
+      <x:c r="A857" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B857" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C857" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D857" s="7">
+        <x:v>46254.5025442477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="858" spans="1:4">
+      <x:c r="A858" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B858" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C858" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D858" s="7">
+        <x:v>46254.5025462847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="859" spans="1:4">
+      <x:c r="A859" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B859" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C859" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D859" s="7">
+        <x:v>46254.5025478241</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="860" spans="1:4">
+      <x:c r="A860" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B860" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C860" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D860" s="7">
+        <x:v>46254.5025494213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="861" spans="1:4">
+      <x:c r="A861" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B861" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C861" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D861" s="7">
+        <x:v>46254.5025510764</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="862" spans="1:4">
+      <x:c r="A862" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B862" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C862" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D862" s="7">
+        <x:v>46254.5025528356</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="863" spans="1:4">
+      <x:c r="A863" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B863" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C863" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D863" s="7">
+        <x:v>46254.502554213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="864" spans="1:4">
+      <x:c r="A864" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B864" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C864" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D864" s="7">
+        <x:v>46254.5025557639</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="865" spans="1:4">
+      <x:c r="A865" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B865" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C865" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D865" s="7">
+        <x:v>46254.5025573264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="866" spans="1:4">
+      <x:c r="A866" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B866" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C866" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D866" s="7">
+        <x:v>46254.5025589583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="867" spans="1:4">
+      <x:c r="A867" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B867" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C867" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D867" s="7">
+        <x:v>46254.5025604977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="868" spans="1:4">
+      <x:c r="A868" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B868" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C868" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D868" s="7">
+        <x:v>46254.5025620139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="869" spans="1:4">
+      <x:c r="A869" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B869" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C869" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D869" s="7">
+        <x:v>46254.5025636574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="870" spans="1:4">
+      <x:c r="A870" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B870" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C870" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D870" s="7">
+        <x:v>46254.5025655787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="871" spans="1:4">
+      <x:c r="A871" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B871" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C871" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D871" s="7">
+        <x:v>46254.5025669792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="872" spans="1:4">
+      <x:c r="A872" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B872" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C872" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D872" s="7">
+        <x:v>46254.5025684259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="873" spans="1:4">
+      <x:c r="A873" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B873" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C873" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D873" s="7">
+        <x:v>46254.5025700231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="874" spans="1:4">
+      <x:c r="A874" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B874" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C874" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D874" s="7">
+        <x:v>46254.5025716551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="875" spans="1:4">
+      <x:c r="A875" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B875" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C875" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D875" s="7">
+        <x:v>46254.5025733333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="876" spans="1:4">
+      <x:c r="A876" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B876" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C876" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D876" s="7">
+        <x:v>46254.5025751157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="877" spans="1:4">
+      <x:c r="A877" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B877" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C877" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D877" s="7">
+        <x:v>46254.5025766088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="878" spans="1:4">
+      <x:c r="A878" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B878" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C878" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D878" s="7">
+        <x:v>46254.5025783681</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="879" spans="1:4">
+      <x:c r="A879" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B879" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C879" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D879" s="7">
+        <x:v>46254.5025798264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="880" spans="1:4">
+      <x:c r="A880" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B880" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C880" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D880" s="7">
+        <x:v>46254.5025813194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="881" spans="1:4">
+      <x:c r="A881" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B881" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C881" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D881" s="7">
+        <x:v>46254.5025831019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="882" spans="1:4">
+      <x:c r="A882" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B882" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C882" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D882" s="7">
+        <x:v>46254.5025847569</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="883" spans="1:4">
+      <x:c r="A883" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B883" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C883" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D883" s="7">
+        <x:v>46254.5025863657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="884" spans="1:4">
+      <x:c r="A884" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B884" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C884" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D884" s="7">
+        <x:v>46254.5025880208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="885" spans="1:4">
+      <x:c r="A885" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B885" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C885" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D885" s="7">
+        <x:v>46254.5025897338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="886" spans="1:4">
+      <x:c r="A886" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B886" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C886" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D886" s="7">
+        <x:v>46254.5025914352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="887" spans="1:4">
+      <x:c r="A887" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B887" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C887" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D887" s="7">
+        <x:v>46254.5025929861</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="888" spans="1:4">
+      <x:c r="A888" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B888" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C888" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D888" s="7">
+        <x:v>46254.5025944676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="889" spans="1:4">
+      <x:c r="A889" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B889" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C889" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D889" s="7">
+        <x:v>46254.5025962153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="890" spans="1:4">
+      <x:c r="A890" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B890" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C890" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D890" s="7">
+        <x:v>46254.502597963</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="891" spans="1:4">
+      <x:c r="A891" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B891" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C891" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D891" s="7">
+        <x:v>46254.5025997685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="892" spans="1:4">
+      <x:c r="A892" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B892" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C892" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D892" s="7">
+        <x:v>46254.5026014005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="893" spans="1:4">
+      <x:c r="A893" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B893" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C893" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D893" s="7">
+        <x:v>46254.5026031597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="894" spans="1:4">
+      <x:c r="A894" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B894" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C894" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D894" s="7">
+        <x:v>46254.502604919</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="895" spans="1:4">
+      <x:c r="A895" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B895" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C895" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D895" s="7">
+        <x:v>46254.5026061458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="896" spans="1:4">
+      <x:c r="A896" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B896" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C896" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D896" s="7">
+        <x:v>46254.5026074421</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="897" spans="1:4">
+      <x:c r="A897" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B897" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C897" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D897" s="7">
+        <x:v>46254.5026091088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="898" spans="1:4">
+      <x:c r="A898" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B898" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C898" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D898" s="7">
+        <x:v>46254.5026109375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="899" spans="1:4">
+      <x:c r="A899" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B899" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C899" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D899" s="7">
+        <x:v>46254.5026127199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="900" spans="1:4">
+      <x:c r="A900" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B900" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C900" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D900" s="7">
+        <x:v>46254.5026143634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="901" spans="1:4">
+      <x:c r="A901" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B901" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C901" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D901" s="7">
+        <x:v>46254.502616088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="902" spans="1:4">
+      <x:c r="A902" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B902" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C902" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D902" s="7">
+        <x:v>46254.5026177199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="903" spans="1:4">
+      <x:c r="A903" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B903" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C903" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D903" s="7">
+        <x:v>46254.5026195833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="904" spans="1:4">
+      <x:c r="A904" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B904" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C904" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D904" s="7">
+        <x:v>46254.5026210648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="905" spans="1:4">
+      <x:c r="A905" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B905" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C905" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D905" s="7">
+        <x:v>46254.5026229745</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="906" spans="1:4">
+      <x:c r="A906" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B906" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C906" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D906" s="7">
+        <x:v>46254.5026247222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="907" spans="1:4">
+      <x:c r="A907" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B907" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C907" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D907" s="7">
+        <x:v>46254.5026264468</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="908" spans="1:4">
+      <x:c r="A908" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B908" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C908" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D908" s="7">
+        <x:v>46254.5026280208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="909" spans="1:4">
+      <x:c r="A909" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B909" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C909" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D909" s="7">
+        <x:v>46254.5026295486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="910" spans="1:4">
+      <x:c r="A910" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B910" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C910" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D910" s="7">
+        <x:v>46254.5026315625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="911" spans="1:4">
+      <x:c r="A911" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B911" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C911" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D911" s="7">
+        <x:v>46254.5026331713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="912" spans="1:4">
+      <x:c r="A912" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B912" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C912" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D912" s="7">
+        <x:v>46254.5026345949</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="913" spans="1:4">
+      <x:c r="A913" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B913" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C913" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D913" s="7">
+        <x:v>46254.5026364931</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="914" spans="1:4">
+      <x:c r="A914" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B914" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C914" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D914" s="7">
+        <x:v>46254.5026380324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="915" spans="1:4">
+      <x:c r="A915" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B915" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C915" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D915" s="7">
+        <x:v>46254.5026395486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="916" spans="1:4">
+      <x:c r="A916" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B916" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C916" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D916" s="7">
+        <x:v>46254.5026413194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="917" spans="1:4">
+      <x:c r="A917" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B917" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C917" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D917" s="7">
+        <x:v>46254.5026429282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="918" spans="1:4">
+      <x:c r="A918" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B918" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C918" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D918" s="7">
+        <x:v>46254.502644838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="919" spans="1:4">
+      <x:c r="A919" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B919" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C919" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D919" s="7">
+        <x:v>46254.5026465972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="920" spans="1:4">
+      <x:c r="A920" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B920" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C920" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D920" s="7">
+        <x:v>46254.5026483449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="921" spans="1:4">
+      <x:c r="A921" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B921" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C921" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D921" s="7">
+        <x:v>46254.502649919</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
+++ b/wwwroot/ChequePrintTracking/Cheque_Print_Tracking_v1.xlsx
@@ -334,6 +334,9 @@
   </x:si>
   <x:si>
     <x:t>Tharak</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -13638,6 +13641,2862 @@
         <x:v>46254.502649919</x:v>
       </x:c>
     </x:row>
+    <x:row r="922" spans="1:4">
+      <x:c r="A922" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B922" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C922" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D922" s="7">
+        <x:v>46254.5047669097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="923" spans="1:4">
+      <x:c r="A923" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B923" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C923" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D923" s="7">
+        <x:v>46254.5047694213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="924" spans="1:4">
+      <x:c r="A924" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B924" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C924" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D924" s="7">
+        <x:v>46254.5047721065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="925" spans="1:4">
+      <x:c r="A925" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B925" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C925" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D925" s="7">
+        <x:v>46254.5047747338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="926" spans="1:4">
+      <x:c r="A926" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B926" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C926" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D926" s="7">
+        <x:v>46254.5047772801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="927" spans="1:4">
+      <x:c r="A927" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B927" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C927" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D927" s="7">
+        <x:v>46254.5047797685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="928" spans="1:4">
+      <x:c r="A928" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B928" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C928" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D928" s="7">
+        <x:v>46254.5047821296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="929" spans="1:4">
+      <x:c r="A929" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B929" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C929" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D929" s="7">
+        <x:v>46254.5047848958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="930" spans="1:4">
+      <x:c r="A930" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B930" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C930" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D930" s="7">
+        <x:v>46254.5047869907</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="931" spans="1:4">
+      <x:c r="A931" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B931" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C931" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D931" s="7">
+        <x:v>46254.5047890972</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="932" spans="1:4">
+      <x:c r="A932" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B932" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C932" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D932" s="7">
+        <x:v>46254.5047915741</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="933" spans="1:4">
+      <x:c r="A933" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B933" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C933" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D933" s="7">
+        <x:v>46254.504793831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="934" spans="1:4">
+      <x:c r="A934" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B934" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C934" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D934" s="7">
+        <x:v>46254.5047963657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="935" spans="1:4">
+      <x:c r="A935" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B935" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C935" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D935" s="7">
+        <x:v>46254.5047987037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="936" spans="1:4">
+      <x:c r="A936" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B936" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C936" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D936" s="7">
+        <x:v>46254.5048010069</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="937" spans="1:4">
+      <x:c r="A937" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B937" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C937" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D937" s="7">
+        <x:v>46254.5048027083</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="938" spans="1:4">
+      <x:c r="A938" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B938" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C938" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D938" s="7">
+        <x:v>46254.5048047801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="939" spans="1:4">
+      <x:c r="A939" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B939" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C939" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D939" s="7">
+        <x:v>46254.5048070255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="940" spans="1:4">
+      <x:c r="A940" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B940" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C940" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D940" s="7">
+        <x:v>46254.5048096296</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="941" spans="1:4">
+      <x:c r="A941" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B941" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C941" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D941" s="7">
+        <x:v>46254.5048116551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="942" spans="1:4">
+      <x:c r="A942" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B942" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C942" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D942" s="7">
+        <x:v>46254.5048140741</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="943" spans="1:4">
+      <x:c r="A943" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B943" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C943" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D943" s="7">
+        <x:v>46254.5048166204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="944" spans="1:4">
+      <x:c r="A944" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B944" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C944" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D944" s="7">
+        <x:v>46254.5048190393</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="945" spans="1:4">
+      <x:c r="A945" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B945" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C945" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D945" s="7">
+        <x:v>46254.5048216898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="946" spans="1:4">
+      <x:c r="A946" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B946" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C946" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D946" s="7">
+        <x:v>46254.5048240046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="947" spans="1:4">
+      <x:c r="A947" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B947" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C947" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D947" s="7">
+        <x:v>46254.5048262384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="948" spans="1:4">
+      <x:c r="A948" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B948" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C948" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D948" s="7">
+        <x:v>46254.5048282407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="949" spans="1:4">
+      <x:c r="A949" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B949" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C949" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D949" s="7">
+        <x:v>46254.5048307292</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="950" spans="1:4">
+      <x:c r="A950" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B950" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C950" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D950" s="7">
+        <x:v>46254.5048332407</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="951" spans="1:4">
+      <x:c r="A951" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B951" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C951" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D951" s="7">
+        <x:v>46254.5048359838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="952" spans="1:4">
+      <x:c r="A952" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B952" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C952" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D952" s="7">
+        <x:v>46254.5048381597</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="953" spans="1:4">
+      <x:c r="A953" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B953" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C953" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D953" s="7">
+        <x:v>46254.5048402546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="954" spans="1:4">
+      <x:c r="A954" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B954" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C954" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D954" s="7">
+        <x:v>46254.5048427431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="955" spans="1:4">
+      <x:c r="A955" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B955" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C955" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D955" s="7">
+        <x:v>46254.5048449537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="956" spans="1:4">
+      <x:c r="A956" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B956" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C956" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D956" s="7">
+        <x:v>46254.5048469097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="957" spans="1:4">
+      <x:c r="A957" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B957" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C957" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D957" s="7">
+        <x:v>46254.5048489699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="958" spans="1:4">
+      <x:c r="A958" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B958" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C958" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D958" s="7">
+        <x:v>46254.5048515394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="959" spans="1:4">
+      <x:c r="A959" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B959" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C959" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D959" s="7">
+        <x:v>46254.5048539815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="960" spans="1:4">
+      <x:c r="A960" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B960" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C960" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D960" s="7">
+        <x:v>46254.5048564005</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="961" spans="1:4">
+      <x:c r="A961" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B961" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C961" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D961" s="7">
+        <x:v>46254.5048589815</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="962" spans="1:4">
+      <x:c r="A962" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B962" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C962" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D962" s="7">
+        <x:v>46254.5048616667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="963" spans="1:4">
+      <x:c r="A963" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B963" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C963" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D963" s="7">
+        <x:v>46254.5048636343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="964" spans="1:4">
+      <x:c r="A964" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B964" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C964" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D964" s="7">
+        <x:v>46254.5048660995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="965" spans="1:4">
+      <x:c r="A965" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B965" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C965" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D965" s="7">
+        <x:v>46254.5048682176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="966" spans="1:4">
+      <x:c r="A966" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B966" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C966" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D966" s="7">
+        <x:v>46254.5048707176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="967" spans="1:4">
+      <x:c r="A967" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B967" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C967" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D967" s="7">
+        <x:v>46254.5048734491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="968" spans="1:4">
+      <x:c r="A968" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B968" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C968" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D968" s="7">
+        <x:v>46254.5048761343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="969" spans="1:4">
+      <x:c r="A969" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B969" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C969" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D969" s="7">
+        <x:v>46254.5048788542</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="970" spans="1:4">
+      <x:c r="A970" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B970" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C970" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D970" s="7">
+        <x:v>46254.5048815046</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="971" spans="1:4">
+      <x:c r="A971" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B971" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C971" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D971" s="7">
+        <x:v>46254.5048839352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="972" spans="1:4">
+      <x:c r="A972" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B972" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C972" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D972" s="7">
+        <x:v>46254.5048863657</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="973" spans="1:4">
+      <x:c r="A973" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B973" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C973" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D973" s="7">
+        <x:v>46254.5048885648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="974" spans="1:4">
+      <x:c r="A974" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B974" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C974" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D974" s="7">
+        <x:v>46254.5048909722</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="975" spans="1:4">
+      <x:c r="A975" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B975" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C975" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D975" s="7">
+        <x:v>46254.504893588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="976" spans="1:4">
+      <x:c r="A976" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B976" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C976" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D976" s="7">
+        <x:v>46254.5048959607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="977" spans="1:4">
+      <x:c r="A977" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B977" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C977" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D977" s="7">
+        <x:v>46254.5048980324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="978" spans="1:4">
+      <x:c r="A978" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B978" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C978" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D978" s="7">
+        <x:v>46254.5049006713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="979" spans="1:4">
+      <x:c r="A979" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B979" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C979" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D979" s="7">
+        <x:v>46254.5049033912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="980" spans="1:4">
+      <x:c r="A980" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B980" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C980" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D980" s="7">
+        <x:v>46254.5049053588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="981" spans="1:4">
+      <x:c r="A981" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B981" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C981" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D981" s="7">
+        <x:v>46254.5049076273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="982" spans="1:4">
+      <x:c r="A982" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B982" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C982" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D982" s="7">
+        <x:v>46254.5049097801</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="983" spans="1:4">
+      <x:c r="A983" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B983" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C983" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D983" s="7">
+        <x:v>46254.5049123958</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="984" spans="1:4">
+      <x:c r="A984" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B984" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C984" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D984" s="7">
+        <x:v>46254.5049152546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="985" spans="1:4">
+      <x:c r="A985" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B985" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C985" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D985" s="7">
+        <x:v>46254.5049179167</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="986" spans="1:4">
+      <x:c r="A986" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B986" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C986" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D986" s="7">
+        <x:v>46254.5049205787</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="987" spans="1:4">
+      <x:c r="A987" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B987" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C987" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D987" s="7">
+        <x:v>46254.5049231481</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="988" spans="1:4">
+      <x:c r="A988" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B988" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C988" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D988" s="7">
+        <x:v>46254.5049255671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="989" spans="1:4">
+      <x:c r="A989" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B989" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C989" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D989" s="7">
+        <x:v>46254.5049276157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="990" spans="1:4">
+      <x:c r="A990" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B990" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C990" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D990" s="7">
+        <x:v>46254.504929919</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="991" spans="1:4">
+      <x:c r="A991" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B991" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C991" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D991" s="7">
+        <x:v>46254.5049320833</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="992" spans="1:4">
+      <x:c r="A992" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B992" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C992" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D992" s="7">
+        <x:v>46254.504934838</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="993" spans="1:4">
+      <x:c r="A993" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B993" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C993" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D993" s="7">
+        <x:v>46254.5049374306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="994" spans="1:4">
+      <x:c r="A994" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B994" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C994" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D994" s="7">
+        <x:v>46254.5049404398</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="995" spans="1:4">
+      <x:c r="A995" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B995" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C995" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D995" s="7">
+        <x:v>46254.5049429282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="996" spans="1:4">
+      <x:c r="A996" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B996" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C996" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D996" s="7">
+        <x:v>46254.504945081</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="997" spans="1:4">
+      <x:c r="A997" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B997" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C997" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D997" s="7">
+        <x:v>46254.5049476273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="998" spans="1:4">
+      <x:c r="A998" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B998" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C998" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D998" s="7">
+        <x:v>46254.5049497685</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="999" spans="1:4">
+      <x:c r="A999" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B999" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C999" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D999" s="7">
+        <x:v>46254.5049522338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1000" spans="1:4">
+      <x:c r="A1000" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B1000" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C1000" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D1000" s="7">
+        <x:v>46254.5049547454</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1001" spans="1:4">
+      <x:c r="A1001" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B1001" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1001" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D1001" s="7">
+        <x:v>46254.5049573032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1002" spans="1:4">
+      <x:c r="A1002" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B1002" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C1002" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D1002" s="7">
+        <x:v>46254.504959537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1003" spans="1:4">
+      <x:c r="A1003" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B1003" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1003" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D1003" s="7">
+        <x:v>46254.5049612616</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1004" spans="1:4">
+      <x:c r="A1004" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B1004" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1004" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D1004" s="7">
+        <x:v>46254.5049634375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1005" spans="1:4">
+      <x:c r="A1005" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B1005" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1005" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D1005" s="7">
+        <x:v>46254.5049651157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1006" spans="1:4">
+      <x:c r="A1006" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B1006" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C1006" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D1006" s="7">
+        <x:v>46254.5049669329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1007" spans="1:4">
+      <x:c r="A1007" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B1007" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C1007" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D1007" s="7">
+        <x:v>46254.5049688194</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1008" spans="1:4">
+      <x:c r="A1008" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B1008" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1008" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D1008" s="7">
+        <x:v>46254.5049708796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1009" spans="1:4">
+      <x:c r="A1009" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B1009" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C1009" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D1009" s="7">
+        <x:v>46254.5049735301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1010" spans="1:4">
+      <x:c r="A1010" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B1010" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C1010" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D1010" s="7">
+        <x:v>46254.5049756134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1011" spans="1:4">
+      <x:c r="A1011" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B1011" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1011" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D1011" s="7">
+        <x:v>46254.5049781019</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1012" spans="1:4">
+      <x:c r="A1012" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B1012" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C1012" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D1012" s="7">
+        <x:v>46254.5049798727</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1013" spans="1:4">
+      <x:c r="A1013" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B1013" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C1013" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D1013" s="7">
+        <x:v>46254.5049816204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1014" spans="1:4">
+      <x:c r="A1014" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B1014" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1014" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D1014" s="7">
+        <x:v>46254.5049835995</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1015" spans="1:4">
+      <x:c r="A1015" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B1015" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1015" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D1015" s="7">
+        <x:v>46254.5049850694</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1016" spans="1:4">
+      <x:c r="A1016" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B1016" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C1016" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D1016" s="7">
+        <x:v>46254.5049869907</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1017" spans="1:4">
+      <x:c r="A1017" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B1017" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C1017" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D1017" s="7">
+        <x:v>46254.5049884259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1018" spans="1:4">
+      <x:c r="A1018" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B1018" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C1018" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D1018" s="7">
+        <x:v>46254.5049898611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1019" spans="1:4">
+      <x:c r="A1019" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B1019" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C1019" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D1019" s="7">
+        <x:v>46254.5049914699</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1020" spans="1:4">
+      <x:c r="A1020" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B1020" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1020" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D1020" s="7">
+        <x:v>46254.5049927431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1021" spans="1:4">
+      <x:c r="A1021" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B1021" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1021" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D1021" s="7">
+        <x:v>46254.504993831</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1022" spans="1:4">
+      <x:c r="A1022" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B1022" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C1022" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D1022" s="7">
+        <x:v>46254.5484793866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1023" spans="1:4">
+      <x:c r="A1023" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B1023" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1023" s="6">
+        <x:v>2000000</x:v>
+      </x:c>
+      <x:c r="D1023" s="7">
+        <x:v>46254.5485007639</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1024" spans="1:4">
+      <x:c r="A1024" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B1024" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1024" s="6">
+        <x:v>200000</x:v>
+      </x:c>
+      <x:c r="D1024" s="7">
+        <x:v>46254.548511713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1025" spans="1:4">
+      <x:c r="A1025" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B1025" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C1025" s="6">
+        <x:v>825812.93</x:v>
+      </x:c>
+      <x:c r="D1025" s="7">
+        <x:v>46254.5485236343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1026" spans="1:4">
+      <x:c r="A1026" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B1026" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C1026" s="6">
+        <x:v>308383.03</x:v>
+      </x:c>
+      <x:c r="D1026" s="7">
+        <x:v>46254.5485342014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1027" spans="1:4">
+      <x:c r="A1027" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B1027" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C1027" s="6">
+        <x:v>1266343.54</x:v>
+      </x:c>
+      <x:c r="D1027" s="7">
+        <x:v>46254.5485416319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1028" spans="1:4">
+      <x:c r="A1028" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1028" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C1028" s="6">
+        <x:v>698750.02</x:v>
+      </x:c>
+      <x:c r="D1028" s="7">
+        <x:v>46254.5485472338</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1029" spans="1:4">
+      <x:c r="A1029" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B1029" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1029" s="6">
+        <x:v>597314.11</x:v>
+      </x:c>
+      <x:c r="D1029" s="7">
+        <x:v>46254.5485505671</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1030" spans="1:4">
+      <x:c r="A1030" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B1030" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C1030" s="6">
+        <x:v>1348177.93</x:v>
+      </x:c>
+      <x:c r="D1030" s="7">
+        <x:v>46254.5485541667</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1031" spans="1:4">
+      <x:c r="A1031" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B1031" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1031" s="6">
+        <x:v>20489.78</x:v>
+      </x:c>
+      <x:c r="D1031" s="7">
+        <x:v>46254.5485596181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1032" spans="1:4">
+      <x:c r="A1032" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B1032" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1032" s="6">
+        <x:v>1021411.3</x:v>
+      </x:c>
+      <x:c r="D1032" s="7">
+        <x:v>46254.5485636227</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1033" spans="1:4">
+      <x:c r="A1033" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B1033" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C1033" s="6">
+        <x:v>2290718.89</x:v>
+      </x:c>
+      <x:c r="D1033" s="7">
+        <x:v>46254.5485661458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1034" spans="1:4">
+      <x:c r="A1034" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B1034" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C1034" s="6">
+        <x:v>291052.41</x:v>
+      </x:c>
+      <x:c r="D1034" s="7">
+        <x:v>46254.5485683333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1035" spans="1:4">
+      <x:c r="A1035" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B1035" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C1035" s="6">
+        <x:v>2421577.69</x:v>
+      </x:c>
+      <x:c r="D1035" s="7">
+        <x:v>46254.5485712153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1036" spans="1:4">
+      <x:c r="A1036" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B1036" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C1036" s="6">
+        <x:v>2919374.18</x:v>
+      </x:c>
+      <x:c r="D1036" s="7">
+        <x:v>46254.5485741088</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1037" spans="1:4">
+      <x:c r="A1037" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B1037" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1037" s="6">
+        <x:v>880241.67</x:v>
+      </x:c>
+      <x:c r="D1037" s="7">
+        <x:v>46254.5485770023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1038" spans="1:4">
+      <x:c r="A1038" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B1038" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1038" s="6">
+        <x:v>1085543.44</x:v>
+      </x:c>
+      <x:c r="D1038" s="7">
+        <x:v>46254.5485794792</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1039" spans="1:4">
+      <x:c r="A1039" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B1039" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1039" s="6">
+        <x:v>138427.33</x:v>
+      </x:c>
+      <x:c r="D1039" s="7">
+        <x:v>46254.5485818403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1040" spans="1:4">
+      <x:c r="A1040" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B1040" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C1040" s="6">
+        <x:v>2955679.34</x:v>
+      </x:c>
+      <x:c r="D1040" s="7">
+        <x:v>46254.5485843287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1041" spans="1:4">
+      <x:c r="A1041" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B1041" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C1041" s="6">
+        <x:v>1140998.55</x:v>
+      </x:c>
+      <x:c r="D1041" s="7">
+        <x:v>46254.5485864236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1042" spans="1:4">
+      <x:c r="A1042" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B1042" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C1042" s="6">
+        <x:v>1095131.7</x:v>
+      </x:c>
+      <x:c r="D1042" s="7">
+        <x:v>46254.548588669</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1043" spans="1:4">
+      <x:c r="A1043" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B1043" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C1043" s="6">
+        <x:v>2010855.35</x:v>
+      </x:c>
+      <x:c r="D1043" s="7">
+        <x:v>46254.5485909375</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1044" spans="1:4">
+      <x:c r="A1044" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B1044" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C1044" s="6">
+        <x:v>514244.81</x:v>
+      </x:c>
+      <x:c r="D1044" s="7">
+        <x:v>46254.5485936343</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1045" spans="1:4">
+      <x:c r="A1045" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B1045" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C1045" s="6">
+        <x:v>1138986.87</x:v>
+      </x:c>
+      <x:c r="D1045" s="7">
+        <x:v>46254.5485960532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1046" spans="1:4">
+      <x:c r="A1046" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B1046" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C1046" s="6">
+        <x:v>973523.92</x:v>
+      </x:c>
+      <x:c r="D1046" s="7">
+        <x:v>46254.5485988426</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1047" spans="1:4">
+      <x:c r="A1047" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B1047" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C1047" s="6">
+        <x:v>97268.63</x:v>
+      </x:c>
+      <x:c r="D1047" s="7">
+        <x:v>46254.5486012847</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1048" spans="1:4">
+      <x:c r="A1048" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B1048" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C1048" s="6">
+        <x:v>199499.63</x:v>
+      </x:c>
+      <x:c r="D1048" s="7">
+        <x:v>46254.5486036806</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1049" spans="1:4">
+      <x:c r="A1049" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B1049" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C1049" s="6">
+        <x:v>944718.96</x:v>
+      </x:c>
+      <x:c r="D1049" s="7">
+        <x:v>46254.5486065162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1050" spans="1:4">
+      <x:c r="A1050" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B1050" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C1050" s="6">
+        <x:v>2743728.22</x:v>
+      </x:c>
+      <x:c r="D1050" s="7">
+        <x:v>46254.5486093981</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1051" spans="1:4">
+      <x:c r="A1051" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B1051" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C1051" s="6">
+        <x:v>419751.33</x:v>
+      </x:c>
+      <x:c r="D1051" s="7">
+        <x:v>46254.5486115741</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1052" spans="1:4">
+      <x:c r="A1052" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B1052" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C1052" s="6">
+        <x:v>2241294.42</x:v>
+      </x:c>
+      <x:c r="D1052" s="7">
+        <x:v>46254.5486144676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1053" spans="1:4">
+      <x:c r="A1053" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B1053" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C1053" s="6">
+        <x:v>1198802.11</x:v>
+      </x:c>
+      <x:c r="D1053" s="7">
+        <x:v>46254.5486169676</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1054" spans="1:4">
+      <x:c r="A1054" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B1054" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C1054" s="6">
+        <x:v>1481053.99</x:v>
+      </x:c>
+      <x:c r="D1054" s="7">
+        <x:v>46254.5486193981</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1055" spans="1:4">
+      <x:c r="A1055" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B1055" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C1055" s="6">
+        <x:v>459371.12</x:v>
+      </x:c>
+      <x:c r="D1055" s="7">
+        <x:v>46254.5486218056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1056" spans="1:4">
+      <x:c r="A1056" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B1056" s="5">
+        <x:v>46256</x:v>
+      </x:c>
+      <x:c r="C1056" s="6">
+        <x:v>1267057.74</x:v>
+      </x:c>
+      <x:c r="D1056" s="7">
+        <x:v>46254.5486242014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1057" spans="1:4">
+      <x:c r="A1057" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B1057" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C1057" s="6">
+        <x:v>1788069.4</x:v>
+      </x:c>
+      <x:c r="D1057" s="7">
+        <x:v>46254.5486265625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1058" spans="1:4">
+      <x:c r="A1058" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B1058" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C1058" s="6">
+        <x:v>2913264.05</x:v>
+      </x:c>
+      <x:c r="D1058" s="7">
+        <x:v>46254.5486302199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1059" spans="1:4">
+      <x:c r="A1059" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B1059" s="5">
+        <x:v>46258</x:v>
+      </x:c>
+      <x:c r="C1059" s="6">
+        <x:v>344540.68</x:v>
+      </x:c>
+      <x:c r="D1059" s="7">
+        <x:v>46254.5486336111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1060" spans="1:4">
+      <x:c r="A1060" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B1060" s="5">
+        <x:v>46243</x:v>
+      </x:c>
+      <x:c r="C1060" s="6">
+        <x:v>2306027.6</x:v>
+      </x:c>
+      <x:c r="D1060" s="7">
+        <x:v>46254.5486362037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1061" spans="1:4">
+      <x:c r="A1061" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B1061" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C1061" s="6">
+        <x:v>1304860.99</x:v>
+      </x:c>
+      <x:c r="D1061" s="7">
+        <x:v>46254.5486391319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1062" spans="1:4">
+      <x:c r="A1062" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B1062" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C1062" s="6">
+        <x:v>2166554.09</x:v>
+      </x:c>
+      <x:c r="D1062" s="7">
+        <x:v>46254.5486418287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1063" spans="1:4">
+      <x:c r="A1063" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B1063" s="5">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="C1063" s="6">
+        <x:v>536776.99</x:v>
+      </x:c>
+      <x:c r="D1063" s="7">
+        <x:v>46254.5486444213</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1064" spans="1:4">
+      <x:c r="A1064" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B1064" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C1064" s="6">
+        <x:v>896035.93</x:v>
+      </x:c>
+      <x:c r="D1064" s="7">
+        <x:v>46254.5486468171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1065" spans="1:4">
+      <x:c r="A1065" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B1065" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C1065" s="6">
+        <x:v>459364.97</x:v>
+      </x:c>
+      <x:c r="D1065" s="7">
+        <x:v>46254.548649537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1066" spans="1:4">
+      <x:c r="A1066" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B1066" s="5">
+        <x:v>46265</x:v>
+      </x:c>
+      <x:c r="C1066" s="6">
+        <x:v>2336100.81</x:v>
+      </x:c>
+      <x:c r="D1066" s="7">
+        <x:v>46254.5486519097</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1067" spans="1:4">
+      <x:c r="A1067" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B1067" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C1067" s="6">
+        <x:v>1797234.81</x:v>
+      </x:c>
+      <x:c r="D1067" s="7">
+        <x:v>46254.5486566898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1068" spans="1:4">
+      <x:c r="A1068" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B1068" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C1068" s="6">
+        <x:v>2787366.75</x:v>
+      </x:c>
+      <x:c r="D1068" s="7">
+        <x:v>46254.5486595023</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1069" spans="1:4">
+      <x:c r="A1069" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B1069" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C1069" s="6">
+        <x:v>723373.91</x:v>
+      </x:c>
+      <x:c r="D1069" s="7">
+        <x:v>46254.5486620255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1070" spans="1:4">
+      <x:c r="A1070" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B1070" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1070" s="6">
+        <x:v>2195990.88</x:v>
+      </x:c>
+      <x:c r="D1070" s="7">
+        <x:v>46254.5486649884</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1071" spans="1:4">
+      <x:c r="A1071" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B1071" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1071" s="6">
+        <x:v>2297737.45</x:v>
+      </x:c>
+      <x:c r="D1071" s="7">
+        <x:v>46254.548667581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1072" spans="1:4">
+      <x:c r="A1072" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B1072" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C1072" s="6">
+        <x:v>2840599.19</x:v>
+      </x:c>
+      <x:c r="D1072" s="7">
+        <x:v>46254.5486723611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1073" spans="1:4">
+      <x:c r="A1073" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B1073" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C1073" s="6">
+        <x:v>2617426.69</x:v>
+      </x:c>
+      <x:c r="D1073" s="7">
+        <x:v>46254.5486754514</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1074" spans="1:4">
+      <x:c r="A1074" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B1074" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C1074" s="6">
+        <x:v>1618348.97</x:v>
+      </x:c>
+      <x:c r="D1074" s="7">
+        <x:v>46254.548679456</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1075" spans="1:4">
+      <x:c r="A1075" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B1075" s="5">
+        <x:v>46244</x:v>
+      </x:c>
+      <x:c r="C1075" s="6">
+        <x:v>1197577.91</x:v>
+      </x:c>
+      <x:c r="D1075" s="7">
+        <x:v>46254.5486822222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1076" spans="1:4">
+      <x:c r="A1076" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B1076" s="5">
+        <x:v>46263</x:v>
+      </x:c>
+      <x:c r="C1076" s="6">
+        <x:v>1553209.95</x:v>
+      </x:c>
+      <x:c r="D1076" s="7">
+        <x:v>46254.5486848495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1077" spans="1:4">
+      <x:c r="A1077" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B1077" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C1077" s="6">
+        <x:v>193013.66</x:v>
+      </x:c>
+      <x:c r="D1077" s="7">
+        <x:v>46254.5486875579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1078" spans="1:4">
+      <x:c r="A1078" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B1078" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1078" s="6">
+        <x:v>691114.08</x:v>
+      </x:c>
+      <x:c r="D1078" s="7">
+        <x:v>46254.5486908912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1079" spans="1:4">
+      <x:c r="A1079" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B1079" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1079" s="6">
+        <x:v>2123815</x:v>
+      </x:c>
+      <x:c r="D1079" s="7">
+        <x:v>46254.5486937037</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1080" spans="1:4">
+      <x:c r="A1080" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B1080" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1080" s="6">
+        <x:v>2716354.62</x:v>
+      </x:c>
+      <x:c r="D1080" s="7">
+        <x:v>46254.5486958796</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1081" spans="1:4">
+      <x:c r="A1081" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B1081" s="5">
+        <x:v>46251</x:v>
+      </x:c>
+      <x:c r="C1081" s="6">
+        <x:v>714775.9</x:v>
+      </x:c>
+      <x:c r="D1081" s="7">
+        <x:v>46254.5486979977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1082" spans="1:4">
+      <x:c r="A1082" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B1082" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1082" s="6">
+        <x:v>397803.23</x:v>
+      </x:c>
+      <x:c r="D1082" s="7">
+        <x:v>46254.5487002662</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1083" spans="1:4">
+      <x:c r="A1083" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B1083" s="5">
+        <x:v>46250</x:v>
+      </x:c>
+      <x:c r="C1083" s="6">
+        <x:v>729748.73</x:v>
+      </x:c>
+      <x:c r="D1083" s="7">
+        <x:v>46254.5487025694</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1084" spans="1:4">
+      <x:c r="A1084" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B1084" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1084" s="6">
+        <x:v>572039.33</x:v>
+      </x:c>
+      <x:c r="D1084" s="7">
+        <x:v>46254.5487046875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1085" spans="1:4">
+      <x:c r="A1085" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B1085" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1085" s="6">
+        <x:v>1063538.4</x:v>
+      </x:c>
+      <x:c r="D1085" s="7">
+        <x:v>46254.5487066898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1086" spans="1:4">
+      <x:c r="A1086" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B1086" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1086" s="6">
+        <x:v>2187498.47</x:v>
+      </x:c>
+      <x:c r="D1086" s="7">
+        <x:v>46254.5487091319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1087" spans="1:4">
+      <x:c r="A1087" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B1087" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C1087" s="6">
+        <x:v>2184912.55</x:v>
+      </x:c>
+      <x:c r="D1087" s="7">
+        <x:v>46254.5487116898</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1088" spans="1:4">
+      <x:c r="A1088" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B1088" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C1088" s="6">
+        <x:v>571436.52</x:v>
+      </x:c>
+      <x:c r="D1088" s="7">
+        <x:v>46254.5487140509</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1089" spans="1:4">
+      <x:c r="A1089" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B1089" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1089" s="6">
+        <x:v>551280.62</x:v>
+      </x:c>
+      <x:c r="D1089" s="7">
+        <x:v>46254.5487164236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1090" spans="1:4">
+      <x:c r="A1090" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B1090" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1090" s="6">
+        <x:v>2769873.53</x:v>
+      </x:c>
+      <x:c r="D1090" s="7">
+        <x:v>46254.5487183912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1091" spans="1:4">
+      <x:c r="A1091" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B1091" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1091" s="6">
+        <x:v>2568044.71</x:v>
+      </x:c>
+      <x:c r="D1091" s="7">
+        <x:v>46254.5487207986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1092" spans="1:4">
+      <x:c r="A1092" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B1092" s="5">
+        <x:v>46255</x:v>
+      </x:c>
+      <x:c r="C1092" s="6">
+        <x:v>2997848.12</x:v>
+      </x:c>
+      <x:c r="D1092" s="7">
+        <x:v>46254.5487229977</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1093" spans="1:4">
+      <x:c r="A1093" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1093" s="5">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="C1093" s="6">
+        <x:v>2260942.95</x:v>
+      </x:c>
+      <x:c r="D1093" s="7">
+        <x:v>46254.5487248727</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1094" spans="1:4">
+      <x:c r="A1094" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B1094" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1094" s="6">
+        <x:v>1457437.74</x:v>
+      </x:c>
+      <x:c r="D1094" s="7">
+        <x:v>46254.5487277199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1095" spans="1:4">
+      <x:c r="A1095" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B1095" s="5">
+        <x:v>46247</x:v>
+      </x:c>
+      <x:c r="C1095" s="6">
+        <x:v>2707426.15</x:v>
+      </x:c>
+      <x:c r="D1095" s="7">
+        <x:v>46254.5487310648</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1096" spans="1:4">
+      <x:c r="A1096" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B1096" s="5">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="C1096" s="6">
+        <x:v>2955941.22</x:v>
+      </x:c>
+      <x:c r="D1096" s="7">
+        <x:v>46254.5487341319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1097" spans="1:4">
+      <x:c r="A1097" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B1097" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C1097" s="6">
+        <x:v>2355602.94</x:v>
+      </x:c>
+      <x:c r="D1097" s="7">
+        <x:v>46254.5487369329</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1098" spans="1:4">
+      <x:c r="A1098" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B1098" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C1098" s="6">
+        <x:v>2871995.6</x:v>
+      </x:c>
+      <x:c r="D1098" s="7">
+        <x:v>46254.5487393171</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1099" spans="1:4">
+      <x:c r="A1099" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B1099" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C1099" s="6">
+        <x:v>1460527.56</x:v>
+      </x:c>
+      <x:c r="D1099" s="7">
+        <x:v>46254.5487420255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1100" spans="1:4">
+      <x:c r="A1100" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B1100" s="5">
+        <x:v>46241</x:v>
+      </x:c>
+      <x:c r="C1100" s="6">
+        <x:v>2906159.39</x:v>
+      </x:c>
+      <x:c r="D1100" s="7">
+        <x:v>46254.5487441204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1101" spans="1:4">
+      <x:c r="A1101" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B1101" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1101" s="6">
+        <x:v>183811.76</x:v>
+      </x:c>
+      <x:c r="D1101" s="7">
+        <x:v>46254.5487464352</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1102" spans="1:4">
+      <x:c r="A1102" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B1102" s="5">
+        <x:v>46236</x:v>
+      </x:c>
+      <x:c r="C1102" s="6">
+        <x:v>1752948.61</x:v>
+      </x:c>
+      <x:c r="D1102" s="7">
+        <x:v>46254.5487484144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1103" spans="1:4">
+      <x:c r="A1103" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B1103" s="5">
+        <x:v>46262</x:v>
+      </x:c>
+      <x:c r="C1103" s="6">
+        <x:v>1593847.28</x:v>
+      </x:c>
+      <x:c r="D1103" s="7">
+        <x:v>46254.5487508912</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1104" spans="1:4">
+      <x:c r="A1104" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B1104" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1104" s="6">
+        <x:v>2554176.29</x:v>
+      </x:c>
+      <x:c r="D1104" s="7">
+        <x:v>46254.5487534028</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1105" spans="1:4">
+      <x:c r="A1105" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B1105" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1105" s="6">
+        <x:v>2025962.45</x:v>
+      </x:c>
+      <x:c r="D1105" s="7">
+        <x:v>46254.5487556713</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1106" spans="1:4">
+      <x:c r="A1106" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B1106" s="5">
+        <x:v>46238</x:v>
+      </x:c>
+      <x:c r="C1106" s="6">
+        <x:v>2824846.79</x:v>
+      </x:c>
+      <x:c r="D1106" s="7">
+        <x:v>46254.5487579282</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1107" spans="1:4">
+      <x:c r="A1107" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B1107" s="5">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="C1107" s="6">
+        <x:v>1783962.94</x:v>
+      </x:c>
+      <x:c r="D1107" s="7">
+        <x:v>46254.5487603009</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1108" spans="1:4">
+      <x:c r="A1108" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B1108" s="5">
+        <x:v>46248</x:v>
+      </x:c>
+      <x:c r="C1108" s="6">
+        <x:v>1972462.12</x:v>
+      </x:c>
+      <x:c r="D1108" s="7">
+        <x:v>46254.5487626968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1109" spans="1:4">
+      <x:c r="A1109" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B1109" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C1109" s="6">
+        <x:v>2804184.07</x:v>
+      </x:c>
+      <x:c r="D1109" s="7">
+        <x:v>46254.5487652546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1110" spans="1:4">
+      <x:c r="A1110" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B1110" s="5">
+        <x:v>46257</x:v>
+      </x:c>
+      <x:c r="C1110" s="6">
+        <x:v>943237.4</x:v>
+      </x:c>
+      <x:c r="D1110" s="7">
+        <x:v>46254.5487673032</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1111" spans="1:4">
+      <x:c r="A1111" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B1111" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1111" s="6">
+        <x:v>2015398.98</x:v>
+      </x:c>
+      <x:c r="D1111" s="7">
+        <x:v>46254.5487696412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1112" spans="1:4">
+      <x:c r="A1112" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B1112" s="5">
+        <x:v>46245</x:v>
+      </x:c>
+      <x:c r="C1112" s="6">
+        <x:v>2787125.98</x:v>
+      </x:c>
+      <x:c r="D1112" s="7">
+        <x:v>46254.548771956</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1113" spans="1:4">
+      <x:c r="A1113" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B1113" s="5">
+        <x:v>46249</x:v>
+      </x:c>
+      <x:c r="C1113" s="6">
+        <x:v>1863856.61</x:v>
+      </x:c>
+      <x:c r="D1113" s="7">
+        <x:v>46254.5487743866</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1114" spans="1:4">
+      <x:c r="A1114" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B1114" s="5">
+        <x:v>46237</x:v>
+      </x:c>
+      <x:c r="C1114" s="6">
+        <x:v>1613365.58</x:v>
+      </x:c>
+      <x:c r="D1114" s="7">
+        <x:v>46254.5487767014</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1115" spans="1:4">
+      <x:c r="A1115" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B1115" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1115" s="6">
+        <x:v>2799844.87</x:v>
+      </x:c>
+      <x:c r="D1115" s="7">
+        <x:v>46254.5487796065</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1116" spans="1:4">
+      <x:c r="A1116" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B1116" s="5">
+        <x:v>46242</x:v>
+      </x:c>
+      <x:c r="C1116" s="6">
+        <x:v>1109211.74</x:v>
+      </x:c>
+      <x:c r="D1116" s="7">
+        <x:v>46254.5487825579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1117" spans="1:4">
+      <x:c r="A1117" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B1117" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C1117" s="6">
+        <x:v>1630110.67</x:v>
+      </x:c>
+      <x:c r="D1117" s="7">
+        <x:v>46254.5487850579</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1118" spans="1:4">
+      <x:c r="A1118" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B1118" s="5">
+        <x:v>46260</x:v>
+      </x:c>
+      <x:c r="C1118" s="6">
+        <x:v>1962274.98</x:v>
+      </x:c>
+      <x:c r="D1118" s="7">
+        <x:v>46254.5487873264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1119" spans="1:4">
+      <x:c r="A1119" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B1119" s="5">
+        <x:v>46261</x:v>
+      </x:c>
+      <x:c r="C1119" s="6">
+        <x:v>1664252.25</x:v>
+      </x:c>
+      <x:c r="D1119" s="7">
+        <x:v>46254.5487893056</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1120" spans="1:4">
+      <x:c r="A1120" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B1120" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1120" s="6">
+        <x:v>794133.3</x:v>
+      </x:c>
+      <x:c r="D1120" s="7">
+        <x:v>46254.5487914583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1121" spans="1:4">
+      <x:c r="A1121" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B1121" s="5">
+        <x:v>46252</x:v>
+      </x:c>
+      <x:c r="C1121" s="6">
+        <x:v>467188.28</x:v>
+      </x:c>
+      <x:c r="D1121" s="7">
+        <x:v>46254.548794537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1122" spans="1:4">
+      <x:c r="A1122" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1122" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1122" s="6">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="D1122" s="7">
+        <x:v>46254.5505903819</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1123" spans="1:4">
+      <x:c r="A1123" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1123" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1123" s="6">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="D1123" s="7">
+        <x:v>46254.5508701968</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1124" spans="1:4">
+      <x:c r="A1124" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B1124" s="5">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="C1124" s="6">
+        <x:v>3773737</x:v>
+      </x:c>
+      <x:c r="D1124" s="7">
+        <x:v>46254.5514982986</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1125" spans="1:4">
+      <x:c r="A1125" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B1125" s="5">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="C1125" s="6">
+        <x:v>303030</x:v>
+      </x:c>
+      <x:c r="D1125" s="7">
+        <x:v>46254.5520629514</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:autoFilter ref="A1:D1"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
